--- a/outputs/q4/q4_partition_candidates.xlsx
+++ b/outputs/q4/q4_partition_candidates.xlsx
@@ -604,7 +604,7 @@
         <v>7</v>
       </c>
       <c r="K2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L2" t="n">
         <v>4</v>
@@ -616,25 +616,25 @@
         <v>3</v>
       </c>
       <c r="O2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8864043267302126</v>
+        <v>0.8825900780064836</v>
       </c>
       <c r="S2" t="n">
-        <v>1.772808653460425</v>
+        <v>1.765180156012967</v>
       </c>
       <c r="T2" t="b">
         <v>1</v>
       </c>
       <c r="U2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -668,16 +668,16 @@
         <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J3" t="n">
         <v>7</v>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M3" t="n">
         <v>2</v>
@@ -686,19 +686,19 @@
         <v>3</v>
       </c>
       <c r="O3" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="P3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="R3" t="n">
-        <v>0.7893141395502672</v>
+        <v>0.7822398536096431</v>
       </c>
       <c r="S3" t="n">
-        <v>1.578628279100534</v>
+        <v>1.564479707219286</v>
       </c>
       <c r="T3" t="b">
         <v>1</v>
@@ -738,7 +738,7 @@
         <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J4" t="n">
         <v>6</v>
@@ -747,7 +747,7 @@
         <v>4</v>
       </c>
       <c r="L4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M4" t="n">
         <v>2</v>
@@ -756,25 +756,25 @@
         <v>3</v>
       </c>
       <c r="O4" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9029098128200543</v>
+        <v>0.8996497756031596</v>
       </c>
       <c r="S4" t="n">
-        <v>1.805819625640109</v>
+        <v>1.799299551206319</v>
       </c>
       <c r="T4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -958,16 +958,16 @@
         <v>3</v>
       </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J2" t="n">
         <v>7</v>
       </c>
       <c r="K2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M2" t="n">
         <v>2</v>
@@ -976,19 +976,19 @@
         <v>3</v>
       </c>
       <c r="O2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="P2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="R2" t="n">
-        <v>1.190790358782802</v>
+        <v>1.183290165105396</v>
       </c>
       <c r="S2" t="n">
-        <v>2.538335928555482</v>
+        <v>2.522834443819205</v>
       </c>
       <c r="T2" t="b">
         <v>1</v>
@@ -1158,12 +1158,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>S001,S002,S003,S004,S005,S006,S007,S008,S009,S011,S014,S015</t>
+          <t>S001,S002,S003,S004,S005,S006,S007,S008,S009,S010,S012,S013,S015</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>S010,S012,S013</t>
+          <t>S011,S014</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1173,10 +1173,10 @@
         <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K2" t="n">
         <v>4</v>
@@ -1185,25 +1185,25 @@
         <v>4</v>
       </c>
       <c r="M2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O2" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="P2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Q2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R2" t="n">
-        <v>0.6318295904444738</v>
+        <v>0.7089065454499904</v>
       </c>
       <c r="S2" t="n">
-        <v>1.263659180888948</v>
+        <v>1.417813090899981</v>
       </c>
       <c r="T2" t="b">
         <v>1</v>
@@ -1228,28 +1228,28 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>S001,S002,S003,S004,S005,S006,S007,S009,S010,S011,S012,S013,S014,S015</t>
+          <t>S001,S002,S003,S004,S005,S006,S007,S008,S009,S011,S014,S015</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>S008</t>
+          <t>S010,S012,S013</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L3" t="n">
         <v>4</v>
@@ -1261,22 +1261,22 @@
         <v>5</v>
       </c>
       <c r="O3" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R3" t="n">
-        <v>0.7738692682094425</v>
+        <v>0.6109989804009428</v>
       </c>
       <c r="S3" t="n">
-        <v>1.547738536418885</v>
+        <v>1.221997960801886</v>
       </c>
       <c r="T3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U3" t="b">
         <v>0</v>
@@ -1298,28 +1298,28 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>S001,S002,S003,S004,S005,S006,S007,S009,S011,S014,S015</t>
+          <t>S001,S002,S003,S004,S005,S006,S007,S008,S009,S015</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>S008,S010,S012,S013</t>
+          <t>S010,S011,S012,S013,S014</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
         <v>3</v>
       </c>
       <c r="J4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L4" t="n">
         <v>4</v>
@@ -1328,25 +1328,25 @@
         <v>4</v>
       </c>
       <c r="N4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O4" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="P4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="Q4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4453786597463259</v>
+        <v>0.4469488239425767</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8907573194926518</v>
+        <v>0.8938976478851535</v>
       </c>
       <c r="T4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U4" t="b">
         <v>0</v>
@@ -1368,55 +1368,55 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>S001,S002,S003,S004,S005,S007,S008,S009,S010,S011,S012,S013,S014,S015</t>
+          <t>S001,S002,S003,S004,S005,S006,S007,S009,S010,S011,S012,S013,S014,S015</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>S006</t>
+          <t>S008</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I5" t="n">
         <v>2</v>
       </c>
       <c r="J5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L5" t="n">
         <v>4</v>
       </c>
       <c r="M5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O5" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="P5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Q5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R5" t="n">
-        <v>0.8864043267302126</v>
+        <v>0.7219030187339267</v>
       </c>
       <c r="S5" t="n">
-        <v>1.772808653460425</v>
+        <v>1.443806037467853</v>
       </c>
       <c r="T5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
@@ -1438,28 +1438,28 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>S001,S002,S003,S004,S005,S007,S008,S009,S011,S014,S015</t>
+          <t>S001,S002,S003,S004,S005,S006,S007,S009,S010,S012,S013,S015</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>S006,S010,S012,S013</t>
+          <t>S008,S011,S014</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>6</v>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L6" t="n">
         <v>4</v>
@@ -1468,25 +1468,25 @@
         <v>4</v>
       </c>
       <c r="N6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O6" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="P6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q6" t="n">
         <v>9</v>
       </c>
       <c r="R6" t="n">
-        <v>0.529042168472513</v>
+        <v>0.4689667193466638</v>
       </c>
       <c r="S6" t="n">
-        <v>1.058084336945026</v>
+        <v>0.9379334386933277</v>
       </c>
       <c r="T6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
@@ -1508,25 +1508,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>S001,S002,S003,S004,S005,S007,S009,S010,S011,S012,S013,S014,S015</t>
+          <t>S001,S002,S003,S004,S005,S006,S007,S009,S011,S014,S015</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>S006,S008</t>
+          <t>S008,S010,S012,S013</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H7" t="n">
         <v>4</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K7" t="n">
         <v>6</v>
@@ -1538,22 +1538,22 @@
         <v>4</v>
       </c>
       <c r="N7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O7" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="P7" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Q7" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6668156867284977</v>
+        <v>0.4514558814308</v>
       </c>
       <c r="S7" t="n">
-        <v>1.333631373456995</v>
+        <v>0.9029117628616</v>
       </c>
       <c r="T7" t="b">
         <v>0</v>
@@ -1578,16 +1578,16 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>S001,S002,S003,S004,S005,S007,S009,S011,S014,S015</t>
+          <t>S001,S002,S003,S004,S005,S006,S007,S009,S015</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>S006,S008,S010,S012,S013</t>
+          <t>S008,S010,S011,S012,S013,S014</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H8" t="n">
         <v>4</v>
@@ -1611,22 +1611,22 @@
         <v>6</v>
       </c>
       <c r="O8" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3479771503859958</v>
+        <v>0.2929157585312748</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6959543007719916</v>
+        <v>0.5858315170625497</v>
       </c>
       <c r="T8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U8" t="b">
         <v>0</v>
@@ -1648,58 +1648,58 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>S001,S002,S004,S005,S006,S008,S009,S010,S012,S013</t>
+          <t>S001,S002,S003,S004,S005,S007,S008,S009,S010,S011,S012,S013,S014,S015</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>S003,S007,S011,S014,S015</t>
+          <t>S006</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J9" t="n">
         <v>7</v>
       </c>
       <c r="K9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O9" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="P9" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="Q9" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2592716219897548</v>
+        <v>0.8825900780064836</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5185432439795097</v>
+        <v>1.765180156012967</v>
       </c>
       <c r="T9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -1718,55 +1718,55 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>S001,S002,S004,S005,S006,S008,S009</t>
+          <t>S001,S002,S003,S004,S005,S007,S008,S009,S010,S012,S013,S015</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>S003,S007,S010,S011,S012,S013,S014,S015</t>
+          <t>S006,S011,S014</t>
         </is>
       </c>
       <c r="G10" t="n">
+        <v>6</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2</v>
+      </c>
+      <c r="J10" t="n">
+        <v>8</v>
+      </c>
+      <c r="K10" t="n">
+        <v>5</v>
+      </c>
+      <c r="L10" t="n">
+        <v>4</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4</v>
+      </c>
+      <c r="O10" t="n">
+        <v>35</v>
+      </c>
+      <c r="P10" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q10" t="n">
         <v>7</v>
       </c>
-      <c r="H10" t="n">
-        <v>4</v>
-      </c>
-      <c r="I10" t="n">
-        <v>3</v>
-      </c>
-      <c r="J10" t="n">
-        <v>9</v>
-      </c>
-      <c r="K10" t="n">
-        <v>6</v>
-      </c>
-      <c r="L10" t="n">
-        <v>5</v>
-      </c>
-      <c r="M10" t="n">
-        <v>4</v>
-      </c>
-      <c r="N10" t="n">
-        <v>6</v>
-      </c>
-      <c r="O10" t="n">
-        <v>44</v>
-      </c>
-      <c r="P10" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>14</v>
-      </c>
       <c r="R10" t="n">
-        <v>0.05061353960151158</v>
+        <v>0.5984830265154518</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1012270792030232</v>
+        <v>1.196966053030904</v>
       </c>
       <c r="T10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U10" t="b">
         <v>0</v>
@@ -1788,31 +1788,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>S001,S002,S004,S005,S006,S009,S010,S012,S013</t>
+          <t>S001,S002,S003,S004,S005,S007,S008,S009,S011,S014,S015</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>S003,S007,S008,S011,S014,S015</t>
+          <t>S006,S010,S012,S013</t>
         </is>
       </c>
       <c r="G11" t="n">
         <v>6</v>
       </c>
       <c r="H11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
         <v>3</v>
       </c>
       <c r="J11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K11" t="n">
         <v>5</v>
       </c>
       <c r="L11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M11" t="n">
         <v>4</v>
@@ -1830,10 +1830,10 @@
         <v>10</v>
       </c>
       <c r="R11" t="n">
-        <v>0.1577745831181424</v>
+        <v>0.5057310899780514</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3155491662362848</v>
+        <v>1.011462179956103</v>
       </c>
       <c r="T11" t="b">
         <v>0</v>
@@ -1858,55 +1858,55 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>S001,S002,S004,S005,S006,S009</t>
+          <t>S001,S002,S003,S004,S005,S007,S008,S009,S015</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>S003,S007,S008,S010,S011,S012,S013,S014,S015</t>
+          <t>S006,S010,S011,S012,S013,S014</t>
         </is>
       </c>
       <c r="G12" t="n">
         <v>7</v>
       </c>
       <c r="H12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I12" t="n">
         <v>3</v>
       </c>
       <c r="J12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K12" t="n">
         <v>5</v>
       </c>
       <c r="L12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M12" t="n">
         <v>4</v>
       </c>
       <c r="N12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O12" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="P12" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Q12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R12" t="n">
-        <v>0.04723446175458641</v>
+        <v>0.3416809335196855</v>
       </c>
       <c r="S12" t="n">
-        <v>0.09446892350917281</v>
+        <v>0.683361867039371</v>
       </c>
       <c r="T12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U12" t="b">
         <v>0</v>
@@ -1928,52 +1928,52 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>S001,S002,S004,S005,S008,S009,S010,S012,S013</t>
+          <t>S001,S002,S003,S004,S005,S007,S009,S010,S011,S012,S013,S014,S015</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>S003,S006,S007,S011,S014,S015</t>
+          <t>S006,S008</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H13" t="n">
         <v>4</v>
       </c>
       <c r="I13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
+        <v>7</v>
+      </c>
+      <c r="K13" t="n">
+        <v>6</v>
+      </c>
+      <c r="L13" t="n">
+        <v>4</v>
+      </c>
+      <c r="M13" t="n">
+        <v>4</v>
+      </c>
+      <c r="N13" t="n">
+        <v>5</v>
+      </c>
+      <c r="O13" t="n">
+        <v>37</v>
+      </c>
+      <c r="P13" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q13" t="n">
         <v>8</v>
       </c>
-      <c r="K13" t="n">
-        <v>6</v>
-      </c>
-      <c r="L13" t="n">
-        <v>5</v>
-      </c>
-      <c r="M13" t="n">
-        <v>4</v>
-      </c>
-      <c r="N13" t="n">
-        <v>5</v>
-      </c>
-      <c r="O13" t="n">
-        <v>41</v>
-      </c>
-      <c r="P13" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>12</v>
-      </c>
       <c r="R13" t="n">
-        <v>0.1613378542437507</v>
+        <v>0.6142702962209006</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3226757084875013</v>
+        <v>1.228540592441801</v>
       </c>
       <c r="T13" t="b">
         <v>0</v>
@@ -1998,55 +1998,55 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>S001,S002,S004,S005,S008,S009</t>
+          <t>S001,S002,S003,S004,S005,S007,S009,S010,S012,S013,S015</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>S003,S006,S007,S010,S011,S012,S013,S014,S015</t>
+          <t>S006,S008,S011,S014</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H14" t="n">
         <v>4</v>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
+        <v>8</v>
+      </c>
+      <c r="K14" t="n">
+        <v>6</v>
+      </c>
+      <c r="L14" t="n">
+        <v>4</v>
+      </c>
+      <c r="M14" t="n">
+        <v>4</v>
+      </c>
+      <c r="N14" t="n">
+        <v>6</v>
+      </c>
+      <c r="O14" t="n">
+        <v>40</v>
+      </c>
+      <c r="P14" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q14" t="n">
         <v>10</v>
       </c>
-      <c r="K14" t="n">
-        <v>6</v>
-      </c>
-      <c r="L14" t="n">
-        <v>5</v>
-      </c>
-      <c r="M14" t="n">
-        <v>4</v>
-      </c>
-      <c r="N14" t="n">
-        <v>6</v>
-      </c>
-      <c r="O14" t="n">
-        <v>45</v>
-      </c>
-      <c r="P14" t="n">
-        <v>18</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>15</v>
-      </c>
       <c r="R14" t="n">
-        <v>0.04379929791328771</v>
+        <v>0.3672345135059796</v>
       </c>
       <c r="S14" t="n">
-        <v>0.08759859582657542</v>
+        <v>0.7344690270119592</v>
       </c>
       <c r="T14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U14" t="b">
         <v>0</v>
@@ -2068,12 +2068,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>S001,S002,S004,S005,S009,S010,S012,S013</t>
+          <t>S001,S002,S003,S004,S005,S007,S009,S011,S014,S015</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>S003,S006,S007,S008,S011,S014,S015</t>
+          <t>S006,S008,S010,S012,S013</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2086,34 +2086,34 @@
         <v>3</v>
       </c>
       <c r="J15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M15" t="n">
         <v>4</v>
       </c>
       <c r="N15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O15" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="P15" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Q15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R15" t="n">
-        <v>0.0598408153721381</v>
+        <v>0.3497236755901159</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1196816307442762</v>
+        <v>0.6994473511802317</v>
       </c>
       <c r="T15" t="b">
         <v>0</v>
@@ -2138,12 +2138,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>S001,S002,S004,S005,S009</t>
+          <t>S001,S002,S003,S004,S005,S007,S009,S015</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>S003,S006,S007,S008,S010,S011,S012,S013,S014,S015</t>
+          <t>S006,S008,S010,S011,S012,S013,S014</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2159,10 +2159,10 @@
         <v>10</v>
       </c>
       <c r="K16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M16" t="n">
         <v>4</v>
@@ -2180,13 +2180,13 @@
         <v>14</v>
       </c>
       <c r="R16" t="n">
-        <v>0.1416472992693857</v>
+        <v>0.1911835526905906</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2832945985387714</v>
+        <v>0.3823671053811813</v>
       </c>
       <c r="T16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U16" t="b">
         <v>0</v>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>S001,S003,S006,S007,S008,S010,S011,S012,S013,S014,S015</t>
+          <t>S001,S006,S008,S010,S011,S012,S013,S014</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>S002,S004,S005,S009</t>
+          <t>S002,S003,S004,S005,S007,S009,S015</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2223,16 +2223,16 @@
         <v>4</v>
       </c>
       <c r="I17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J17" t="n">
         <v>10</v>
       </c>
       <c r="K17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M17" t="n">
         <v>4</v>
@@ -2241,22 +2241,22 @@
         <v>6</v>
       </c>
       <c r="O17" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="P17" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q17" t="n">
         <v>17</v>
       </c>
-      <c r="Q17" t="n">
-        <v>14</v>
-      </c>
       <c r="R17" t="n">
-        <v>0.2223419226000759</v>
+        <v>0.1042330674917164</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4446838452001518</v>
+        <v>0.2084661349834329</v>
       </c>
       <c r="T17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U17" t="b">
         <v>0</v>
@@ -2278,12 +2278,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>S001,S003,S006,S007,S008,S011,S014,S015</t>
+          <t>S001,S006,S008,S010,S012,S013</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>S002,S004,S005,S009,S010,S012,S013</t>
+          <t>S002,S003,S004,S005,S007,S009,S011,S014,S015</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2293,40 +2293,40 @@
         <v>4</v>
       </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M18" t="n">
         <v>4</v>
       </c>
       <c r="N18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O18" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="P18" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="Q18" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="R18" t="n">
-        <v>0.02386314594965132</v>
+        <v>0.2627731903912418</v>
       </c>
       <c r="S18" t="n">
-        <v>0.04772629189930264</v>
+        <v>0.5255463807824835</v>
       </c>
       <c r="T18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U18" t="b">
         <v>0</v>
@@ -2348,31 +2348,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>S001,S003,S006,S007,S010,S011,S012,S013,S014,S015</t>
+          <t>S001,S006,S008,S011,S014</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>S002,S004,S005,S008,S009</t>
+          <t>S002,S003,S004,S005,S007,S009,S010,S012,S013,S015</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H19" t="n">
         <v>4</v>
       </c>
       <c r="I19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K19" t="n">
         <v>6</v>
       </c>
       <c r="L19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M19" t="n">
         <v>4</v>
@@ -2381,19 +2381,19 @@
         <v>6</v>
       </c>
       <c r="O19" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="P19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R19" t="n">
-        <v>0.1244939212439778</v>
+        <v>0.2802840283071055</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2489878424879557</v>
+        <v>0.5605680566142109</v>
       </c>
       <c r="T19" t="b">
         <v>0</v>
@@ -2418,31 +2418,31 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>S001,S003,S006,S007,S011,S014,S015</t>
+          <t>S001,S006,S008</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>S002,S004,S005,S008,S009,S010,S012,S013</t>
+          <t>S002,S003,S004,S005,S007,S009,S010,S011,S012,S013,S014,S015</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H20" t="n">
         <v>4</v>
       </c>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K20" t="n">
         <v>6</v>
       </c>
       <c r="L20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M20" t="n">
         <v>4</v>
@@ -2460,10 +2460,10 @@
         <v>12</v>
       </c>
       <c r="R20" t="n">
-        <v>0.07763389292196132</v>
+        <v>0.522276641227914</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1552677858439226</v>
+        <v>1.044553282455828</v>
       </c>
       <c r="T20" t="b">
         <v>0</v>
@@ -2488,52 +2488,52 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>S001,S003,S007,S008,S010,S011,S012,S013,S014,S015</t>
+          <t>S001,S006,S010,S011,S012,S013,S014</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>S002,S004,S005,S006,S009</t>
+          <t>S002,S003,S004,S005,S007,S008,S009,S015</t>
         </is>
       </c>
       <c r="G21" t="n">
         <v>7</v>
       </c>
       <c r="H21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K21" t="n">
         <v>5</v>
       </c>
       <c r="L21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M21" t="n">
         <v>4</v>
       </c>
       <c r="N21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O21" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="P21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q21" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="R21" t="n">
-        <v>0.1279290850852766</v>
+        <v>0.2517084997904261</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2558581701705532</v>
+        <v>0.5034169995808523</v>
       </c>
       <c r="T21" t="b">
         <v>0</v>
@@ -2558,31 +2558,31 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>S001,S003,S007,S008,S011,S014,S015</t>
+          <t>S001,S006,S010,S012,S013</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>S002,S004,S005,S006,S009,S010,S012,S013</t>
+          <t>S002,S003,S004,S005,S007,S008,S009,S011,S014,S015</t>
         </is>
       </c>
       <c r="G22" t="n">
         <v>6</v>
       </c>
       <c r="H22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J22" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K22" t="n">
         <v>5</v>
       </c>
       <c r="L22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M22" t="n">
         <v>4</v>
@@ -2591,22 +2591,22 @@
         <v>5</v>
       </c>
       <c r="O22" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="P22" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Q22" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="R22" t="n">
-        <v>0.07407062179635307</v>
+        <v>0.4157586562487923</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1481412435927061</v>
+        <v>0.8315173124975845</v>
       </c>
       <c r="T22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U22" t="b">
         <v>0</v>
@@ -2628,52 +2628,52 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>S001,S003,S007,S010,S011,S012,S013,S014,S015</t>
+          <t>S001,S006,S011,S014</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>S002,S004,S005,S006,S008,S009</t>
+          <t>S002,S003,S004,S005,S007,S008,S009,S010,S012,S013,S015</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N23" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O23" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="P23" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="Q23" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="R23" t="n">
-        <v>0.03008108372917862</v>
+        <v>0.504104078675067</v>
       </c>
       <c r="S23" t="n">
-        <v>0.06016216745835724</v>
+        <v>1.008208157350134</v>
       </c>
       <c r="T23" t="b">
         <v>0</v>
@@ -2698,52 +2698,52 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>S001,S003,S007,S011,S014,S015</t>
+          <t>S001,S006</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>S002,S004,S005,S006,S008,S009,S010,S012,S013</t>
+          <t>S002,S003,S004,S005,S007,S008,S009,S010,S011,S012,S013,S014,S015</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J24" t="n">
         <v>7</v>
       </c>
       <c r="K24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O24" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="P24" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="Q24" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="R24" t="n">
-        <v>0.1755676606679656</v>
+        <v>0.7822398536096431</v>
       </c>
       <c r="S24" t="n">
-        <v>0.3511353213359312</v>
+        <v>1.564479707219286</v>
       </c>
       <c r="T24" t="b">
         <v>0</v>
@@ -2768,16 +2768,16 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>S001,S006,S008,S010,S012,S013</t>
+          <t>S001,S008,S010,S011,S012,S013,S014</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>S002,S003,S004,S005,S007,S009,S011,S014,S015</t>
+          <t>S002,S003,S004,S005,S006,S007,S009,S015</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H25" t="n">
         <v>4</v>
@@ -2792,7 +2792,7 @@
         <v>6</v>
       </c>
       <c r="L25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M25" t="n">
         <v>4</v>
@@ -2801,19 +2801,19 @@
         <v>6</v>
       </c>
       <c r="O25" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="P25" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="Q25" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="R25" t="n">
-        <v>0.264728110143555</v>
+        <v>0.2059652733324006</v>
       </c>
       <c r="S25" t="n">
-        <v>0.5294562202871099</v>
+        <v>0.4119305466648013</v>
       </c>
       <c r="T25" t="b">
         <v>0</v>
@@ -2838,52 +2838,52 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>S001,S006,S008</t>
+          <t>S001,S008,S010,S012,S013</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>S002,S003,S004,S005,S007,S009,S010,S011,S012,S013,S014,S015</t>
+          <t>S002,S003,S004,S005,S006,S007,S009,S011,S014,S015</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H26" t="n">
         <v>4</v>
       </c>
       <c r="I26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K26" t="n">
         <v>6</v>
       </c>
       <c r="L26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M26" t="n">
         <v>4</v>
       </c>
       <c r="N26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O26" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="P26" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="Q26" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="R26" t="n">
-        <v>0.575317023398396</v>
+        <v>0.3645053962319259</v>
       </c>
       <c r="S26" t="n">
-        <v>1.150634046796792</v>
+        <v>0.7290107924638518</v>
       </c>
       <c r="T26" t="b">
         <v>0</v>
@@ -2908,52 +2908,52 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>S001,S006,S010,S012,S013</t>
+          <t>S001,S008,S011,S014</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>S002,S003,S004,S005,S007,S008,S009,S011,S014,S015</t>
+          <t>S002,S003,S004,S005,S006,S007,S009,S010,S012,S013,S015</t>
         </is>
       </c>
       <c r="G27" t="n">
         <v>6</v>
       </c>
       <c r="H27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I27" t="n">
         <v>4</v>
       </c>
       <c r="J27" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K27" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M27" t="n">
         <v>4</v>
       </c>
       <c r="N27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O27" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="P27" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q27" t="n">
         <v>13</v>
       </c>
-      <c r="Q27" t="n">
-        <v>11</v>
-      </c>
       <c r="R27" t="n">
-        <v>0.4411897903691649</v>
+        <v>0.3820162341477896</v>
       </c>
       <c r="S27" t="n">
-        <v>0.8823795807383298</v>
+        <v>0.7640324682955792</v>
       </c>
       <c r="T27" t="b">
         <v>0</v>
@@ -2978,55 +2978,55 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>S001,S006</t>
+          <t>S001,S008</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>S002,S003,S004,S005,S007,S008,S009,S010,S011,S012,S013,S014,S015</t>
+          <t>S002,S003,S004,S005,S006,S007,S009,S010,S011,S012,S013,S014,S015</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K28" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N28" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O28" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="P28" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="Q28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="R28" t="n">
-        <v>0.7893141395502672</v>
+        <v>0.6299093637409401</v>
       </c>
       <c r="S28" t="n">
-        <v>1.578628279100534</v>
+        <v>1.25981872748188</v>
       </c>
       <c r="T28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U28" t="b">
         <v>0</v>
@@ -3048,52 +3048,52 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>S001,S008,S010,S012,S013</t>
+          <t>S001,S010,S011,S012,S013,S014</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>S002,S003,S004,S005,S006,S007,S009,S011,S014,S015</t>
+          <t>S002,S003,S004,S005,S006,S007,S008,S009,S015</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H29" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I29" t="n">
         <v>4</v>
       </c>
       <c r="J29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K29" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M29" t="n">
         <v>4</v>
       </c>
       <c r="N29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O29" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="P29" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Q29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R29" t="n">
-        <v>0.3621296195038851</v>
+        <v>0.3569763902133176</v>
       </c>
       <c r="S29" t="n">
-        <v>0.7242592390077701</v>
+        <v>0.7139527804266351</v>
       </c>
       <c r="T29" t="b">
         <v>0</v>
@@ -3118,31 +3118,31 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>S001,S008</t>
+          <t>S001,S010,S012,S013</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>S002,S003,S004,S005,S006,S007,S009,S010,S011,S012,S013,S014,S015</t>
+          <t>S002,S003,S004,S005,S006,S007,S008,S009,S011,S014,S015</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H30" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J30" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K30" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M30" t="n">
         <v>4</v>
@@ -3151,19 +3151,19 @@
         <v>5</v>
       </c>
       <c r="O30" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="P30" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q30" t="n">
         <v>10</v>
       </c>
-      <c r="Q30" t="n">
-        <v>8</v>
-      </c>
       <c r="R30" t="n">
-        <v>0.6823706048793409</v>
+        <v>0.5210265466716836</v>
       </c>
       <c r="S30" t="n">
-        <v>1.364741209758682</v>
+        <v>1.042053093343367</v>
       </c>
       <c r="T30" t="b">
         <v>0</v>
@@ -3188,12 +3188,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>S001,S010,S012,S013</t>
+          <t>S001,S011,S014</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>S002,S003,S004,S005,S006,S007,S008,S009,S011,S014,S015</t>
+          <t>S002,S003,S004,S005,S006,S007,S008,S009,S010,S012,S013,S015</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -3206,34 +3206,34 @@
         <v>4</v>
       </c>
       <c r="J31" t="n">
+        <v>7</v>
+      </c>
+      <c r="K31" t="n">
+        <v>4</v>
+      </c>
+      <c r="L31" t="n">
+        <v>6</v>
+      </c>
+      <c r="M31" t="n">
+        <v>3</v>
+      </c>
+      <c r="N31" t="n">
+        <v>4</v>
+      </c>
+      <c r="O31" t="n">
+        <v>36</v>
+      </c>
+      <c r="P31" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q31" t="n">
         <v>8</v>
       </c>
-      <c r="K31" t="n">
-        <v>4</v>
-      </c>
-      <c r="L31" t="n">
-        <v>5</v>
-      </c>
-      <c r="M31" t="n">
-        <v>4</v>
-      </c>
-      <c r="N31" t="n">
-        <v>5</v>
-      </c>
-      <c r="O31" t="n">
-        <v>38</v>
-      </c>
-      <c r="P31" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>9</v>
-      </c>
       <c r="R31" t="n">
-        <v>0.5439772123411258</v>
+        <v>0.6145275976096061</v>
       </c>
       <c r="S31" t="n">
-        <v>1.087954424682252</v>
+        <v>1.229055195219212</v>
       </c>
       <c r="T31" t="b">
         <v>0</v>
@@ -3273,7 +3273,7 @@
         <v>2</v>
       </c>
       <c r="I32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J32" t="n">
         <v>6</v>
@@ -3282,7 +3282,7 @@
         <v>4</v>
       </c>
       <c r="L32" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M32" t="n">
         <v>2</v>
@@ -3291,25 +3291,25 @@
         <v>3</v>
       </c>
       <c r="O32" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="P32" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q32" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R32" t="n">
-        <v>0.9029098128200543</v>
+        <v>0.8996497756031596</v>
       </c>
       <c r="S32" t="n">
-        <v>1.805819625640109</v>
+        <v>1.799299551206319</v>
       </c>
       <c r="T32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3473,60 +3473,60 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>S001,S002,S003,S004,S005,S006,S007,S009,S011,S014,S015</t>
+          <t>S001,S002,S003,S004,S005,S006,S007,S008,S009,S015</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>S008</t>
+          <t>S010,S012,S013</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>S010,S012,S013</t>
+          <t>S011,S014</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
         <v>3</v>
       </c>
       <c r="J2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L2" t="n">
         <v>4</v>
       </c>
       <c r="M2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O2" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="P2" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Q2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8305867880178948</v>
+        <v>0.7480246607610628</v>
       </c>
       <c r="S2" t="n">
-        <v>1.859454196164898</v>
+        <v>1.660003997317204</v>
       </c>
       <c r="T2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U2" t="b">
         <v>0</v>
@@ -3548,57 +3548,57 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>S001,S002,S003,S004,S005,S007,S008,S009,S011,S014,S015</t>
+          <t>S001,S002,S003,S004,S005,S006,S007,S009,S010,S012,S013,S015</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>S006</t>
+          <t>S008</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>S010,S012,S013</t>
+          <t>S011,S014</t>
         </is>
       </c>
       <c r="G3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J3" t="n">
         <v>7</v>
       </c>
-      <c r="H3" t="n">
-        <v>3</v>
-      </c>
-      <c r="I3" t="n">
-        <v>3</v>
-      </c>
-      <c r="J3" t="n">
-        <v>9</v>
-      </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L3" t="n">
         <v>4</v>
       </c>
       <c r="M3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O3" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="P3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q3" t="n">
         <v>10</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9290121060386071</v>
+        <v>0.8509739720139744</v>
       </c>
       <c r="S3" t="n">
-        <v>2.139382119750829</v>
+        <v>1.809172873892032</v>
       </c>
       <c r="T3" t="b">
         <v>1</v>
@@ -3623,21 +3623,21 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>S001,S002,S003,S004,S005,S007,S009,S011,S014,S015</t>
+          <t>S001,S002,S003,S004,S005,S006,S007,S009,S015</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>S006,S008</t>
+          <t>S008,S010,S012,S013</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>S010,S012,S013</t>
+          <t>S011,S014</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H4" t="n">
         <v>4</v>
@@ -3655,7 +3655,7 @@
         <v>4</v>
       </c>
       <c r="M4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N4" t="n">
         <v>7</v>
@@ -3670,13 +3670,13 @@
         <v>16</v>
       </c>
       <c r="R4" t="n">
-        <v>0.723181407515105</v>
+        <v>0.6148991849051111</v>
       </c>
       <c r="S4" t="n">
-        <v>1.567249668083908</v>
+        <v>1.457215157369799</v>
       </c>
       <c r="T4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U4" t="b">
         <v>0</v>
@@ -3698,57 +3698,57 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>S001,S002,S003,S004,S005,S007,S009,S010,S011,S012,S013,S014,S015</t>
+          <t>S001,S002,S003,S004,S005,S006,S007,S009,S011,S014,S015</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>S006</t>
+          <t>S008</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>S008</t>
+          <t>S010,S012,S013</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J5" t="n">
+        <v>8</v>
+      </c>
+      <c r="K5" t="n">
+        <v>6</v>
+      </c>
+      <c r="L5" t="n">
+        <v>4</v>
+      </c>
+      <c r="M5" t="n">
+        <v>6</v>
+      </c>
+      <c r="N5" t="n">
         <v>7</v>
       </c>
-      <c r="K5" t="n">
-        <v>6</v>
-      </c>
-      <c r="L5" t="n">
-        <v>4</v>
-      </c>
-      <c r="M5" t="n">
-        <v>4</v>
-      </c>
-      <c r="N5" t="n">
-        <v>5</v>
-      </c>
       <c r="O5" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="P5" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="Q5" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="R5" t="n">
-        <v>1.063321486202158</v>
+        <v>0.7687899072026257</v>
       </c>
       <c r="S5" t="n">
-        <v>2.339643157871329</v>
+        <v>1.705932550409486</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
@@ -3773,24 +3773,24 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>S001,S002,S003,S004,S005,S007,S009,S011,S014,S015</t>
+          <t>S001,S002,S003,S004,S005,S006,S007,S009,S015</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>S006,S010,S012,S013</t>
+          <t>S008,S011,S014</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>S008</t>
+          <t>S010,S012,S013</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
         <v>3</v>
@@ -3808,22 +3808,22 @@
         <v>6</v>
       </c>
       <c r="N6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O6" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="P6" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Q6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="R6" t="n">
-        <v>0.737498395312136</v>
+        <v>0.5464999305099193</v>
       </c>
       <c r="S6" t="n">
-        <v>1.713351932124403</v>
+        <v>1.250493349740166</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -3848,24 +3848,24 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>S001,S002,S003,S004,S005,S007,S009,S011,S014,S015</t>
+          <t>S001,S002,S003,S004,S005,S006,S007,S009,S015</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>S006</t>
+          <t>S008</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>S008,S010,S012,S013</t>
+          <t>S010,S011,S012,S013,S014</t>
         </is>
       </c>
       <c r="G7" t="n">
         <v>7</v>
       </c>
       <c r="H7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I7" t="n">
         <v>3</v>
@@ -3880,25 +3880,25 @@
         <v>4</v>
       </c>
       <c r="M7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O7" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="P7" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="Q7" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="R7" t="n">
-        <v>0.774984330351202</v>
+        <v>0.6256145721777332</v>
       </c>
       <c r="S7" t="n">
-        <v>1.875863461538498</v>
+        <v>1.478389430412091</v>
       </c>
       <c r="T7" t="b">
         <v>0</v>
@@ -3923,60 +3923,60 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>S001,S002,S004,S005,S006,S008,S009</t>
+          <t>S001,S002,S003,S004,S005,S007,S008,S009,S010,S012,S013,S015</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>S003,S007,S011,S014,S015</t>
+          <t>S006</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>S010,S012,S013</t>
+          <t>S011,S014</t>
         </is>
       </c>
       <c r="G8" t="n">
+        <v>7</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J8" t="n">
         <v>8</v>
       </c>
-      <c r="H8" t="n">
-        <v>4</v>
-      </c>
-      <c r="I8" t="n">
-        <v>4</v>
-      </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
+        <v>5</v>
+      </c>
+      <c r="L8" t="n">
+        <v>4</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3</v>
+      </c>
+      <c r="N8" t="n">
+        <v>4</v>
+      </c>
+      <c r="O8" t="n">
+        <v>36</v>
+      </c>
+      <c r="P8" t="n">
         <v>9</v>
       </c>
-      <c r="K8" t="n">
-        <v>6</v>
-      </c>
-      <c r="L8" t="n">
-        <v>5</v>
-      </c>
-      <c r="M8" t="n">
-        <v>6</v>
-      </c>
-      <c r="N8" t="n">
-        <v>7</v>
-      </c>
-      <c r="O8" t="n">
-        <v>49</v>
-      </c>
-      <c r="P8" t="n">
-        <v>22</v>
-      </c>
       <c r="Q8" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4151448044171708</v>
+        <v>0.9945137274845971</v>
       </c>
       <c r="S8" t="n">
-        <v>1.01637478344381</v>
+        <v>2.23208926137137</v>
       </c>
       <c r="T8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U8" t="b">
         <v>0</v>
@@ -3998,57 +3998,57 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>S001,S002,S004,S005,S006,S009</t>
+          <t>S001,S002,S003,S004,S005,S007,S008,S009,S015</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>S003,S007,S008,S011,S014,S015</t>
+          <t>S006,S010,S012,S013</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>S010,S012,S013</t>
+          <t>S011,S014</t>
         </is>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K9" t="n">
         <v>5</v>
       </c>
       <c r="L9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O9" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="P9" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="Q9" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3750457192858483</v>
+        <v>0.6517882784113355</v>
       </c>
       <c r="S9" t="n">
-        <v>0.8767836915573183</v>
+        <v>1.510578492650091</v>
       </c>
       <c r="T9" t="b">
         <v>0</v>
@@ -4073,57 +4073,57 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>S001,S002,S004,S005,S006,S009,S010,S012,S013</t>
+          <t>S001,S002,S003,S004,S005,S007,S008,S009,S011,S014,S015</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>S003,S007,S011,S014,S015</t>
+          <t>S006</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>S008</t>
+          <t>S010,S012,S013</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H10" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I10" t="n">
         <v>3</v>
       </c>
       <c r="J10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O10" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="P10" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="Q10" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="R10" t="n">
-        <v>0.5545557733816414</v>
+        <v>0.9067645383434788</v>
       </c>
       <c r="S10" t="n">
-        <v>1.354974926801687</v>
+        <v>2.10069479933274</v>
       </c>
       <c r="T10" t="b">
         <v>0</v>
@@ -4148,60 +4148,60 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>S001,S002,S004,S005,S006,S009</t>
+          <t>S001,S002,S003,S004,S005,S007,S008,S009,S015</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>S003,S007,S010,S011,S012,S013,S014,S015</t>
+          <t>S006,S011,S014</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>S008</t>
+          <t>S010,S012,S013</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H11" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
         <v>3</v>
       </c>
       <c r="J11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K11" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O11" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="P11" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="Q11" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="R11" t="n">
-        <v>0.5058079821445296</v>
+        <v>0.6395792294191169</v>
       </c>
       <c r="S11" t="n">
-        <v>1.075384441337207</v>
+        <v>1.361152987982978</v>
       </c>
       <c r="T11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U11" t="b">
         <v>0</v>
@@ -4223,57 +4223,57 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>S001,S002,S004,S005,S006,S009</t>
+          <t>S001,S002,S003,S004,S005,S007,S008,S009,S015</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>S003,S007,S011,S014,S015</t>
+          <t>S006</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>S008,S010,S012,S013</t>
+          <t>S010,S011,S012,S013,S014</t>
         </is>
       </c>
       <c r="G12" t="n">
         <v>8</v>
       </c>
       <c r="H12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O12" t="n">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="P12" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="Q12" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="R12" t="n">
-        <v>0.2315140053428556</v>
+        <v>0.7666752862830063</v>
       </c>
       <c r="S12" t="n">
-        <v>0.5649832706404149</v>
+        <v>1.854619564645192</v>
       </c>
       <c r="T12" t="b">
         <v>0</v>
@@ -4298,60 +4298,60 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>S001,S002,S004,S005,S008,S009</t>
+          <t>S001,S002,S003,S004,S005,S007,S009,S010,S012,S013,S015</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>S003,S006,S007,S011,S014,S015</t>
+          <t>S006,S008</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>S010,S012,S013</t>
+          <t>S011,S014</t>
         </is>
       </c>
       <c r="G13" t="n">
+        <v>7</v>
+      </c>
+      <c r="H13" t="n">
+        <v>4</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2</v>
+      </c>
+      <c r="J13" t="n">
         <v>8</v>
       </c>
-      <c r="H13" t="n">
-        <v>4</v>
-      </c>
-      <c r="I13" t="n">
-        <v>4</v>
-      </c>
-      <c r="J13" t="n">
-        <v>10</v>
-      </c>
       <c r="K13" t="n">
         <v>6</v>
       </c>
       <c r="L13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O13" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="P13" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="Q13" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="R13" t="n">
-        <v>0.3759410152264748</v>
+        <v>0.7454057394432181</v>
       </c>
       <c r="S13" t="n">
-        <v>0.881684336075041</v>
+        <v>1.648579054406929</v>
       </c>
       <c r="T13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U13" t="b">
         <v>0</v>
@@ -4373,17 +4373,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>S001,S002,S004,S005,S009</t>
+          <t>S001,S002,S003,S004,S005,S007,S009,S015</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>S003,S006,S007,S008,S011,S014,S015</t>
+          <t>S006,S008,S010,S012,S013</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>S010,S012,S013</t>
+          <t>S011,S014</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -4393,40 +4393,40 @@
         <v>4</v>
       </c>
       <c r="I14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J14" t="n">
         <v>10</v>
       </c>
       <c r="K14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N14" t="n">
         <v>7</v>
       </c>
       <c r="O14" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="P14" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q14" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="R14" t="n">
-        <v>0.3670347558512174</v>
+        <v>0.5384827936511233</v>
       </c>
       <c r="S14" t="n">
-        <v>0.8105787787218842</v>
+        <v>1.312547643779211</v>
       </c>
       <c r="T14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U14" t="b">
         <v>0</v>
@@ -4448,36 +4448,36 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>S001,S002,S004,S005,S009,S010,S012,S013</t>
+          <t>S001,S002,S003,S004,S005,S007,S009,S011,S014,S015</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>S003,S006,S007,S011,S014,S015</t>
+          <t>S006,S008</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>S008</t>
+          <t>S010,S012,S013</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H15" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I15" t="n">
         <v>3</v>
       </c>
       <c r="J15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M15" t="n">
         <v>6</v>
@@ -4486,19 +4486,19 @@
         <v>7</v>
       </c>
       <c r="O15" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="P15" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Q15" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="R15" t="n">
-        <v>0.5150040330184545</v>
+        <v>0.6627178437302658</v>
       </c>
       <c r="S15" t="n">
-        <v>1.215426375714121</v>
+        <v>1.413912295879005</v>
       </c>
       <c r="T15" t="b">
         <v>0</v>
@@ -4523,24 +4523,24 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>S001,S002,S004,S005,S009</t>
+          <t>S001,S002,S003,S004,S005,S007,S009,S015</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>S003,S006,S007,S010,S011,S012,S013,S014,S015</t>
+          <t>S006,S008,S011,S014</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>S008</t>
+          <t>S010,S012,S013</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H16" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I16" t="n">
         <v>3</v>
@@ -4549,10 +4549,10 @@
         <v>10</v>
       </c>
       <c r="K16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M16" t="n">
         <v>6</v>
@@ -4561,22 +4561,22 @@
         <v>8</v>
       </c>
       <c r="O16" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="P16" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="Q16" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="R16" t="n">
-        <v>0.5172211004762033</v>
+        <v>0.4641110193292764</v>
       </c>
       <c r="S16" t="n">
-        <v>1.205334803473102</v>
+        <v>1.111760330362134</v>
       </c>
       <c r="T16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U16" t="b">
         <v>0</v>
@@ -4598,57 +4598,57 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>S001,S002,S004,S005,S009</t>
+          <t>S001,S002,S003,S004,S005,S007,S009,S015</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>S003,S006,S007,S011,S014,S015</t>
+          <t>S006,S008</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>S008,S010,S012,S013</t>
+          <t>S010,S011,S012,S013,S014</t>
         </is>
       </c>
       <c r="G17" t="n">
         <v>8</v>
       </c>
       <c r="H17" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J17" t="n">
         <v>10</v>
       </c>
       <c r="K17" t="n">
+        <v>6</v>
+      </c>
+      <c r="L17" t="n">
+        <v>4</v>
+      </c>
+      <c r="M17" t="n">
+        <v>6</v>
+      </c>
+      <c r="N17" t="n">
         <v>7</v>
       </c>
-      <c r="L17" t="n">
-        <v>5</v>
-      </c>
-      <c r="M17" t="n">
-        <v>6</v>
-      </c>
-      <c r="N17" t="n">
-        <v>8</v>
-      </c>
       <c r="O17" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="P17" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="Q17" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="R17" t="n">
-        <v>0.1917898891585989</v>
+        <v>0.511565908274876</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4364993408512393</v>
+        <v>1.18636917588161</v>
       </c>
       <c r="T17" t="b">
         <v>0</v>
@@ -4673,36 +4673,36 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>S001,S002,S004,S005,S008,S009,S010,S012,S013</t>
+          <t>S001,S002,S003,S004,S005,S007,S009,S010,S011,S012,S013,S014,S015</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>S003,S007,S011,S014,S015</t>
+          <t>S006</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>S006</t>
+          <t>S008</t>
         </is>
       </c>
       <c r="G18" t="n">
+        <v>5</v>
+      </c>
+      <c r="H18" t="n">
+        <v>5</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2</v>
+      </c>
+      <c r="J18" t="n">
         <v>7</v>
       </c>
-      <c r="H18" t="n">
-        <v>5</v>
-      </c>
-      <c r="I18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J18" t="n">
-        <v>8</v>
-      </c>
       <c r="K18" t="n">
         <v>6</v>
       </c>
       <c r="L18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M18" t="n">
         <v>4</v>
@@ -4711,19 +4711,19 @@
         <v>5</v>
       </c>
       <c r="O18" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="P18" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="Q18" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6559202492800263</v>
+        <v>1.010491708231437</v>
       </c>
       <c r="S18" t="n">
-        <v>1.59510612974662</v>
+        <v>2.259956360561812</v>
       </c>
       <c r="T18" t="b">
         <v>0</v>
@@ -4748,57 +4748,57 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>S001,S002,S004,S005,S008,S009</t>
+          <t>S001,S002,S003,S004,S005,S007,S009,S010,S012,S013,S015</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>S003,S007,S010,S011,S012,S013,S014,S015</t>
+          <t>S006,S011,S014</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>S006</t>
+          <t>S008</t>
         </is>
       </c>
       <c r="G19" t="n">
+        <v>6</v>
+      </c>
+      <c r="H19" t="n">
+        <v>5</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2</v>
+      </c>
+      <c r="J19" t="n">
         <v>8</v>
       </c>
-      <c r="H19" t="n">
-        <v>5</v>
-      </c>
-      <c r="I19" t="n">
-        <v>3</v>
-      </c>
-      <c r="J19" t="n">
-        <v>10</v>
-      </c>
       <c r="K19" t="n">
         <v>6</v>
       </c>
       <c r="L19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N19" t="n">
         <v>6</v>
       </c>
       <c r="O19" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="P19" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Q19" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6069811885964967</v>
+        <v>0.7459511494311634</v>
       </c>
       <c r="S19" t="n">
-        <v>1.29268179685787</v>
+        <v>1.656574565131006</v>
       </c>
       <c r="T19" t="b">
         <v>0</v>
@@ -4823,57 +4823,57 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>S001,S002,S004,S005,S008,S009</t>
+          <t>S001,S002,S003,S004,S005,S007,S009,S010,S012,S013,S015</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>S003,S007,S011,S014,S015</t>
+          <t>S006</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>S006,S010,S012,S013</t>
+          <t>S008,S011,S014</t>
         </is>
       </c>
       <c r="G20" t="n">
+        <v>7</v>
+      </c>
+      <c r="H20" t="n">
+        <v>5</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2</v>
+      </c>
+      <c r="J20" t="n">
         <v>8</v>
       </c>
-      <c r="H20" t="n">
-        <v>5</v>
-      </c>
-      <c r="I20" t="n">
-        <v>4</v>
-      </c>
-      <c r="J20" t="n">
-        <v>10</v>
-      </c>
       <c r="K20" t="n">
         <v>6</v>
       </c>
       <c r="L20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O20" t="n">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="P20" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="Q20" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="R20" t="n">
-        <v>0.3052467365786499</v>
+        <v>0.7881985798905259</v>
       </c>
       <c r="S20" t="n">
-        <v>0.7469938887062725</v>
+        <v>1.898253461497943</v>
       </c>
       <c r="T20" t="b">
         <v>0</v>
@@ -4898,57 +4898,57 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>S001,S002,S004,S005,S009,S010,S012,S013</t>
+          <t>S001,S002,S003,S004,S005,S007,S009,S011,S014,S015</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>S003,S007,S008,S011,S014,S015</t>
+          <t>S006,S010,S012,S013</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>S006</t>
+          <t>S008</t>
         </is>
       </c>
       <c r="G21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H21" t="n">
+        <v>5</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3</v>
+      </c>
+      <c r="J21" t="n">
+        <v>9</v>
+      </c>
+      <c r="K21" t="n">
+        <v>6</v>
+      </c>
+      <c r="L21" t="n">
+        <v>4</v>
+      </c>
+      <c r="M21" t="n">
+        <v>6</v>
+      </c>
+      <c r="N21" t="n">
         <v>7</v>
       </c>
-      <c r="H21" t="n">
-        <v>5</v>
-      </c>
-      <c r="I21" t="n">
-        <v>3</v>
-      </c>
-      <c r="J21" t="n">
-        <v>8</v>
-      </c>
-      <c r="K21" t="n">
-        <v>5</v>
-      </c>
-      <c r="L21" t="n">
-        <v>5</v>
-      </c>
-      <c r="M21" t="n">
-        <v>4</v>
-      </c>
-      <c r="N21" t="n">
-        <v>5</v>
-      </c>
       <c r="O21" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="P21" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="Q21" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6177765957258087</v>
+        <v>0.6745320554935893</v>
       </c>
       <c r="S21" t="n">
-        <v>1.442860571439201</v>
+        <v>1.559922423144246</v>
       </c>
       <c r="T21" t="b">
         <v>0</v>
@@ -4973,21 +4973,21 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>S001,S002,S004,S005,S009</t>
+          <t>S001,S002,S003,S004,S005,S007,S009,S015</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>S003,S007,S008,S010,S011,S012,S013,S014,S015</t>
+          <t>S006,S010,S011,S012,S013,S014</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>S006</t>
+          <t>S008</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H22" t="n">
         <v>5</v>
@@ -4999,31 +4999,31 @@
         <v>10</v>
       </c>
       <c r="K22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M22" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O22" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="P22" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Q22" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6178894484203183</v>
+        <v>0.5474004919664507</v>
       </c>
       <c r="S22" t="n">
-        <v>1.429232436359681</v>
+        <v>1.33237930314685</v>
       </c>
       <c r="T22" t="b">
         <v>0</v>
@@ -5048,17 +5048,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>S001,S002,S004,S005,S009</t>
+          <t>S001,S002,S003,S004,S005,S007,S009,S015</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>S003,S007,S008,S011,S014,S015</t>
+          <t>S006,S010,S012,S013</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>S006,S010,S012,S013</t>
+          <t>S008,S011,S014</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5068,22 +5068,22 @@
         <v>5</v>
       </c>
       <c r="I23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J23" t="n">
         <v>10</v>
       </c>
       <c r="K23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M23" t="n">
         <v>6</v>
       </c>
       <c r="N23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O23" t="n">
         <v>50</v>
@@ -5095,10 +5095,10 @@
         <v>20</v>
       </c>
       <c r="R23" t="n">
-        <v>0.2720736006829309</v>
+        <v>0.4425346642657214</v>
       </c>
       <c r="S23" t="n">
-        <v>0.6074027968197812</v>
+        <v>0.9730273109841009</v>
       </c>
       <c r="T23" t="b">
         <v>1</v>
@@ -5123,57 +5123,57 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>S001,S002,S004,S005,S009,S010,S012,S013</t>
+          <t>S001,S002,S003,S004,S005,S007,S009,S011,S014,S015</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>S003,S007,S011,S014,S015</t>
+          <t>S006</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>S006,S008</t>
+          <t>S008,S010,S012,S013</t>
         </is>
       </c>
       <c r="G24" t="n">
         <v>7</v>
       </c>
       <c r="H24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I24" t="n">
         <v>3</v>
       </c>
       <c r="J24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M24" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O24" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="P24" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="Q24" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="R24" t="n">
-        <v>0.4409740498803741</v>
+        <v>0.7744372596459465</v>
       </c>
       <c r="S24" t="n">
-        <v>1.075877824626554</v>
+        <v>1.871987204624148</v>
       </c>
       <c r="T24" t="b">
         <v>0</v>
@@ -5198,24 +5198,24 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>S001,S002,S004,S005,S009</t>
+          <t>S001,S002,S003,S004,S005,S007,S009,S015</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>S003,S007,S010,S011,S012,S013,S014,S015</t>
+          <t>S006,S011,S014</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>S006,S008</t>
+          <t>S008,S010,S012,S013</t>
         </is>
       </c>
       <c r="G25" t="n">
         <v>8</v>
       </c>
       <c r="H25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I25" t="n">
         <v>3</v>
@@ -5224,34 +5224,34 @@
         <v>10</v>
       </c>
       <c r="K25" t="n">
+        <v>6</v>
+      </c>
+      <c r="L25" t="n">
+        <v>4</v>
+      </c>
+      <c r="M25" t="n">
+        <v>5</v>
+      </c>
+      <c r="N25" t="n">
         <v>7</v>
       </c>
-      <c r="L25" t="n">
-        <v>5</v>
-      </c>
-      <c r="M25" t="n">
-        <v>6</v>
-      </c>
-      <c r="N25" t="n">
-        <v>8</v>
-      </c>
       <c r="O25" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="P25" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="Q25" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="R25" t="n">
-        <v>0.4139184733417461</v>
+        <v>0.50151005792555</v>
       </c>
       <c r="S25" t="n">
-        <v>0.9357868364312587</v>
+        <v>1.167880130188624</v>
       </c>
       <c r="T25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U25" t="b">
         <v>0</v>
@@ -5273,57 +5273,57 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>S001,S002,S004,S005,S009</t>
+          <t>S001,S002,S003,S004,S005,S007,S009,S015</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>S003,S007,S011,S014,S015</t>
+          <t>S006</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>S006,S008,S010,S012,S013</t>
+          <t>S008,S010,S011,S012,S013,S014</t>
         </is>
       </c>
       <c r="G26" t="n">
         <v>8</v>
       </c>
       <c r="H26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J26" t="n">
         <v>10</v>
       </c>
       <c r="K26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M26" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N26" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O26" t="n">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="P26" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="Q26" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="R26" t="n">
-        <v>0.1273183708710454</v>
+        <v>0.6685258909192622</v>
       </c>
       <c r="S26" t="n">
-        <v>0.3080154110620637</v>
+        <v>1.63417702027486</v>
       </c>
       <c r="T26" t="b">
         <v>0</v>
@@ -5348,17 +5348,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>S001,S003,S006,S007,S008,S011,S014,S015</t>
+          <t>S001,S006,S008,S010,S012,S013</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>S002,S004,S005,S009</t>
+          <t>S002,S003,S004,S005,S007,S009,S015</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>S010,S012,S013</t>
+          <t>S011,S014</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5368,37 +5368,37 @@
         <v>4</v>
       </c>
       <c r="I27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J27" t="n">
         <v>10</v>
       </c>
       <c r="K27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N27" t="n">
         <v>7</v>
       </c>
       <c r="O27" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="P27" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Q27" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="R27" t="n">
-        <v>0.3857532912206075</v>
+        <v>0.4865700378002026</v>
       </c>
       <c r="S27" t="n">
-        <v>0.9256986628685849</v>
+        <v>1.188900364186009</v>
       </c>
       <c r="T27" t="b">
         <v>0</v>
@@ -5423,57 +5423,57 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>S001,S003,S006,S007,S011,S014,S015</t>
+          <t>S001,S006,S008</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>S002,S004,S005,S008,S009</t>
+          <t>S002,S003,S004,S005,S007,S009,S010,S012,S013,S015</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>S010,S012,S013</t>
+          <t>S011,S014</t>
         </is>
       </c>
       <c r="G28" t="n">
+        <v>7</v>
+      </c>
+      <c r="H28" t="n">
+        <v>4</v>
+      </c>
+      <c r="I28" t="n">
+        <v>4</v>
+      </c>
+      <c r="J28" t="n">
         <v>8</v>
       </c>
-      <c r="H28" t="n">
-        <v>4</v>
-      </c>
-      <c r="I28" t="n">
-        <v>3</v>
-      </c>
-      <c r="J28" t="n">
-        <v>10</v>
-      </c>
       <c r="K28" t="n">
         <v>6</v>
       </c>
       <c r="L28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O28" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="P28" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="Q28" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="R28" t="n">
-        <v>0.3660552638328921</v>
+        <v>0.6604535044122442</v>
       </c>
       <c r="S28" t="n">
-        <v>0.7861075709820933</v>
+        <v>1.518153326608618</v>
       </c>
       <c r="T28" t="b">
         <v>0</v>
@@ -5498,36 +5498,36 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>S001,S003,S006,S007,S010,S011,S012,S013,S014,S015</t>
+          <t>S001,S006,S008,S011,S014</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>S002,S004,S005,S009</t>
+          <t>S002,S003,S004,S005,S007,S009,S015</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>S008</t>
+          <t>S010,S012,S013</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H29" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J29" t="n">
         <v>10</v>
       </c>
       <c r="K29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M29" t="n">
         <v>6</v>
@@ -5536,19 +5536,19 @@
         <v>8</v>
       </c>
       <c r="O29" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="P29" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R29" t="n">
-        <v>0.5446953084684037</v>
+        <v>0.4056775540536631</v>
       </c>
       <c r="S29" t="n">
-        <v>1.320526085943483</v>
+        <v>0.9931852611562655</v>
       </c>
       <c r="T29" t="b">
         <v>0</v>
@@ -5573,36 +5573,36 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>S001,S003,S006,S007,S011,S014,S015</t>
+          <t>S001,S006,S008</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>S002,S004,S005,S009,S010,S012,S013</t>
+          <t>S002,S003,S004,S005,S007,S009,S011,S014,S015</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>S008</t>
+          <t>S010,S012,S013</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H30" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K30" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M30" t="n">
         <v>6</v>
@@ -5611,19 +5611,19 @@
         <v>7</v>
       </c>
       <c r="O30" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="P30" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Q30" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="R30" t="n">
-        <v>0.4996527695657563</v>
+        <v>0.5761465309048989</v>
       </c>
       <c r="S30" t="n">
-        <v>1.096154271805692</v>
+        <v>1.272824964431536</v>
       </c>
       <c r="T30" t="b">
         <v>0</v>
@@ -5648,57 +5648,57 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>S001,S003,S006,S007,S011,S014,S015</t>
+          <t>S001,S006,S008</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>S002,S004,S005,S009</t>
+          <t>S002,S003,S004,S005,S007,S009,S015</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>S008,S010,S012,S013</t>
+          <t>S010,S011,S012,S013,S014</t>
         </is>
       </c>
       <c r="G31" t="n">
         <v>8</v>
       </c>
       <c r="H31" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I31" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J31" t="n">
         <v>10</v>
       </c>
       <c r="K31" t="n">
+        <v>6</v>
+      </c>
+      <c r="L31" t="n">
+        <v>6</v>
+      </c>
+      <c r="M31" t="n">
+        <v>6</v>
+      </c>
+      <c r="N31" t="n">
         <v>7</v>
       </c>
-      <c r="L31" t="n">
-        <v>5</v>
-      </c>
-      <c r="M31" t="n">
-        <v>6</v>
-      </c>
-      <c r="N31" t="n">
-        <v>8</v>
-      </c>
       <c r="O31" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="P31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R31" t="n">
-        <v>0.1996426124978302</v>
+        <v>0.416389677626978</v>
       </c>
       <c r="S31" t="n">
-        <v>0.4784854934250467</v>
+        <v>0.9367795537015149</v>
       </c>
       <c r="T31" t="b">
         <v>0</v>
@@ -5723,42 +5723,42 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>S001,S003,S007,S008,S011,S014,S015</t>
+          <t>S001,S006,S010,S012,S013</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>S002,S004,S005,S006,S009</t>
+          <t>S002,S003,S004,S005,S007,S008,S009,S015</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>S010,S012,S013</t>
+          <t>S011,S014</t>
         </is>
       </c>
       <c r="G32" t="n">
         <v>8</v>
       </c>
       <c r="H32" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K32" t="n">
         <v>5</v>
       </c>
       <c r="L32" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M32" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N32" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O32" t="n">
         <v>47</v>
@@ -5770,13 +5770,13 @@
         <v>17</v>
       </c>
       <c r="R32" t="n">
-        <v>0.3661643296532231</v>
+        <v>0.5773086137235207</v>
       </c>
       <c r="S32" t="n">
-        <v>0.791008215499816</v>
+        <v>1.382864559539872</v>
       </c>
       <c r="T32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U32" t="b">
         <v>0</v>
@@ -5798,57 +5798,57 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>S001,S003,S007,S011,S014,S015</t>
+          <t>S001,S006</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>S002,S004,S005,S006,S008,S009</t>
+          <t>S002,S003,S004,S005,S007,S008,S009,S010,S012,S013,S015</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>S010,S012,S013</t>
+          <t>S011,S014</t>
         </is>
       </c>
       <c r="G33" t="n">
+        <v>7</v>
+      </c>
+      <c r="H33" t="n">
+        <v>3</v>
+      </c>
+      <c r="I33" t="n">
+        <v>4</v>
+      </c>
+      <c r="J33" t="n">
         <v>8</v>
       </c>
-      <c r="H33" t="n">
-        <v>4</v>
-      </c>
-      <c r="I33" t="n">
-        <v>3</v>
-      </c>
-      <c r="J33" t="n">
-        <v>9</v>
-      </c>
       <c r="K33" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M33" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N33" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O33" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="P33" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="Q33" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="R33" t="n">
-        <v>0.3799157182268371</v>
+        <v>0.8898069435975667</v>
       </c>
       <c r="S33" t="n">
-        <v>0.9012548992971092</v>
+        <v>1.948952417850216</v>
       </c>
       <c r="T33" t="b">
         <v>0</v>
@@ -5873,57 +5873,57 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>S001,S003,S007,S010,S011,S012,S013,S014,S015</t>
+          <t>S001,S006,S011,S014</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>S002,S004,S005,S006,S009</t>
+          <t>S002,S003,S004,S005,S007,S008,S009,S015</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>S008</t>
+          <t>S010,S012,S013</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H34" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I34" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J34" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K34" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M34" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N34" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O34" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="P34" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Q34" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="R34" t="n">
-        <v>0.5141179920506962</v>
+        <v>0.5514012653273935</v>
       </c>
       <c r="S34" t="n">
-        <v>1.185752102422561</v>
+        <v>1.224594699198576</v>
       </c>
       <c r="T34" t="b">
         <v>0</v>
@@ -5948,57 +5948,57 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>S001,S003,S007,S011,S014,S015</t>
+          <t>S001,S006</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>S002,S004,S005,S006,S009,S010,S012,S013</t>
+          <t>S002,S003,S004,S005,S007,S008,S009,S011,S014,S015</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>S008</t>
+          <t>S010,S012,S013</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H35" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I35" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J35" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K35" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M35" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N35" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O35" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="P35" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="Q35" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="R35" t="n">
-        <v>0.5193876293478553</v>
+        <v>0.8033429296543581</v>
       </c>
       <c r="S35" t="n">
-        <v>1.235702822893258</v>
+        <v>1.830777498144963</v>
       </c>
       <c r="T35" t="b">
         <v>0</v>
@@ -6023,57 +6023,57 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>S001,S003,S007,S011,S014,S015</t>
+          <t>S001,S006</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>S002,S004,S005,S006,S009</t>
+          <t>S002,S003,S004,S005,S007,S008,S009,S015</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>S008,S010,S012,S013</t>
+          <t>S010,S011,S012,S013,S014</t>
         </is>
       </c>
       <c r="G36" t="n">
         <v>8</v>
       </c>
       <c r="H36" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I36" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J36" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K36" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L36" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M36" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N36" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O36" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="P36" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="Q36" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="R36" t="n">
-        <v>0.1945762029422239</v>
+        <v>0.6580797193128287</v>
       </c>
       <c r="S36" t="n">
-        <v>0.455168095169609</v>
+        <v>1.584702263457414</v>
       </c>
       <c r="T36" t="b">
         <v>0</v>
@@ -6098,57 +6098,57 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>S001,S003,S007,S008,S010,S011,S012,S013,S014,S015</t>
+          <t>S001,S006,S010,S011,S012,S013,S014</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>S002,S004,S005,S009</t>
+          <t>S002,S003,S004,S005,S007,S009,S015</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>S006</t>
+          <t>S008</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H37" t="n">
         <v>5</v>
       </c>
       <c r="I37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J37" t="n">
         <v>10</v>
       </c>
       <c r="K37" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L37" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M37" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N37" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O37" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="P37" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="Q37" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="R37" t="n">
-        <v>0.6437526059447748</v>
+        <v>0.4937223946847512</v>
       </c>
       <c r="S37" t="n">
-        <v>1.550274371355716</v>
+        <v>1.207584492056803</v>
       </c>
       <c r="T37" t="b">
         <v>0</v>
@@ -6173,60 +6173,60 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>S001,S003,S007,S008,S011,S014,S015</t>
+          <t>S001,S006,S010,S012,S013</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>S002,S004,S005,S009,S010,S012,S013</t>
+          <t>S002,S003,S004,S005,S007,S009,S011,S014,S015</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>S006</t>
+          <t>S008</t>
         </is>
       </c>
       <c r="G38" t="n">
+        <v>6</v>
+      </c>
+      <c r="H38" t="n">
+        <v>5</v>
+      </c>
+      <c r="I38" t="n">
+        <v>4</v>
+      </c>
+      <c r="J38" t="n">
+        <v>9</v>
+      </c>
+      <c r="K38" t="n">
+        <v>6</v>
+      </c>
+      <c r="L38" t="n">
+        <v>6</v>
+      </c>
+      <c r="M38" t="n">
+        <v>6</v>
+      </c>
+      <c r="N38" t="n">
         <v>7</v>
       </c>
-      <c r="H38" t="n">
-        <v>5</v>
-      </c>
-      <c r="I38" t="n">
-        <v>3</v>
-      </c>
-      <c r="J38" t="n">
-        <v>8</v>
-      </c>
-      <c r="K38" t="n">
-        <v>5</v>
-      </c>
-      <c r="L38" t="n">
-        <v>5</v>
-      </c>
-      <c r="M38" t="n">
-        <v>4</v>
-      </c>
-      <c r="N38" t="n">
-        <v>5</v>
-      </c>
       <c r="O38" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="P38" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="Q38" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="R38" t="n">
-        <v>0.6040153521150139</v>
+        <v>0.6010377670302034</v>
       </c>
       <c r="S38" t="n">
-        <v>1.317304629456517</v>
+        <v>1.435127612054198</v>
       </c>
       <c r="T38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U38" t="b">
         <v>0</v>
@@ -6248,17 +6248,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>S001,S003,S007,S008,S011,S014,S015</t>
+          <t>S001,S006,S010,S012,S013</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>S002,S004,S005,S009</t>
+          <t>S002,S003,S004,S005,S007,S009,S015</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>S006,S010,S012,S013</t>
+          <t>S008,S011,S014</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6268,37 +6268,37 @@
         <v>5</v>
       </c>
       <c r="I39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J39" t="n">
         <v>10</v>
       </c>
       <c r="K39" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L39" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M39" t="n">
         <v>6</v>
       </c>
       <c r="N39" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O39" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="P39" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="Q39" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="R39" t="n">
-        <v>0.2788872557304052</v>
+        <v>0.3581793404736414</v>
       </c>
       <c r="S39" t="n">
-        <v>0.6563177681310476</v>
+        <v>0.7816771147129822</v>
       </c>
       <c r="T39" t="b">
         <v>1</v>
@@ -6323,57 +6323,57 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>S001,S003,S007,S010,S011,S012,S013,S014,S015</t>
+          <t>S001,S006,S011,S014</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>S002,S004,S005,S008,S009</t>
+          <t>S002,S003,S004,S005,S007,S009,S010,S012,S013,S015</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>S006</t>
+          <t>S008</t>
         </is>
       </c>
       <c r="G40" t="n">
+        <v>6</v>
+      </c>
+      <c r="H40" t="n">
+        <v>5</v>
+      </c>
+      <c r="I40" t="n">
+        <v>4</v>
+      </c>
+      <c r="J40" t="n">
         <v>8</v>
       </c>
-      <c r="H40" t="n">
-        <v>5</v>
-      </c>
-      <c r="I40" t="n">
-        <v>3</v>
-      </c>
-      <c r="J40" t="n">
-        <v>10</v>
-      </c>
       <c r="K40" t="n">
         <v>6</v>
       </c>
       <c r="L40" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M40" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N40" t="n">
         <v>6</v>
       </c>
       <c r="O40" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="P40" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q40" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R40" t="n">
-        <v>0.6143034980058845</v>
+        <v>0.6615946235951956</v>
       </c>
       <c r="S40" t="n">
-        <v>1.403502369321569</v>
+        <v>1.526148837332694</v>
       </c>
       <c r="T40" t="b">
         <v>0</v>
@@ -6398,36 +6398,36 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>S001,S003,S007,S011,S014,S015</t>
+          <t>S001,S006</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>S002,S004,S005,S008,S009,S010,S012,S013</t>
+          <t>S002,S003,S004,S005,S007,S009,S010,S011,S012,S013,S014,S015</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>S006</t>
+          <t>S008</t>
         </is>
       </c>
       <c r="G41" t="n">
+        <v>5</v>
+      </c>
+      <c r="H41" t="n">
+        <v>5</v>
+      </c>
+      <c r="I41" t="n">
+        <v>4</v>
+      </c>
+      <c r="J41" t="n">
         <v>7</v>
       </c>
-      <c r="H41" t="n">
-        <v>5</v>
-      </c>
-      <c r="I41" t="n">
-        <v>3</v>
-      </c>
-      <c r="J41" t="n">
-        <v>8</v>
-      </c>
       <c r="K41" t="n">
         <v>6</v>
       </c>
       <c r="L41" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M41" t="n">
         <v>4</v>
@@ -6436,19 +6436,19 @@
         <v>5</v>
       </c>
       <c r="O41" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P41" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q41" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R41" t="n">
-        <v>0.6228409782052479</v>
+        <v>0.9087827548486003</v>
       </c>
       <c r="S41" t="n">
-        <v>1.469550187763936</v>
+        <v>1.983975395582852</v>
       </c>
       <c r="T41" t="b">
         <v>0</v>
@@ -6473,57 +6473,57 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>S001,S003,S007,S011,S014,S015</t>
+          <t>S001,S006</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>S002,S004,S005,S008,S009</t>
+          <t>S002,S003,S004,S005,S007,S009,S010,S012,S013,S015</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>S006,S010,S012,S013</t>
+          <t>S008,S011,S014</t>
         </is>
       </c>
       <c r="G42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H42" t="n">
+        <v>5</v>
+      </c>
+      <c r="I42" t="n">
+        <v>4</v>
+      </c>
+      <c r="J42" t="n">
         <v>8</v>
       </c>
-      <c r="H42" t="n">
-        <v>5</v>
-      </c>
-      <c r="I42" t="n">
-        <v>3</v>
-      </c>
-      <c r="J42" t="n">
-        <v>10</v>
-      </c>
       <c r="K42" t="n">
         <v>6</v>
       </c>
       <c r="L42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M42" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O42" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="P42" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="Q42" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="R42" t="n">
-        <v>0.2747787236626313</v>
+        <v>0.6837715423650159</v>
       </c>
       <c r="S42" t="n">
-        <v>0.6318740045595721</v>
+        <v>1.637402005901321</v>
       </c>
       <c r="T42" t="b">
         <v>0</v>
@@ -6548,57 +6548,57 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>S001,S003,S007,S010,S011,S012,S013,S014,S015</t>
+          <t>S001,S006,S011,S014</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>S002,S004,S005,S009</t>
+          <t>S002,S003,S004,S005,S007,S009,S015</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>S006,S008</t>
+          <t>S008,S010,S012,S013</t>
         </is>
       </c>
       <c r="G43" t="n">
         <v>8</v>
       </c>
       <c r="H43" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I43" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J43" t="n">
         <v>10</v>
       </c>
       <c r="K43" t="n">
+        <v>6</v>
+      </c>
+      <c r="L43" t="n">
+        <v>6</v>
+      </c>
+      <c r="M43" t="n">
+        <v>5</v>
+      </c>
+      <c r="N43" t="n">
         <v>7</v>
       </c>
-      <c r="L43" t="n">
-        <v>5</v>
-      </c>
-      <c r="M43" t="n">
-        <v>6</v>
-      </c>
-      <c r="N43" t="n">
-        <v>8</v>
-      </c>
       <c r="O43" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="P43" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q43" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R43" t="n">
-        <v>0.4360664584589815</v>
+        <v>0.4067365699997597</v>
       </c>
       <c r="S43" t="n">
-        <v>1.05097811890164</v>
+        <v>0.9205855710022196</v>
       </c>
       <c r="T43" t="b">
         <v>0</v>
@@ -6623,57 +6623,57 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>S001,S003,S007,S011,S014,S015</t>
+          <t>S001,S006</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>S002,S004,S005,S009,S010,S012,S013</t>
+          <t>S002,S003,S004,S005,S007,S009,S011,S014,S015</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>S006,S008</t>
+          <t>S008,S010,S012,S013</t>
         </is>
       </c>
       <c r="G44" t="n">
         <v>7</v>
       </c>
       <c r="H44" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I44" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J44" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K44" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L44" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M44" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N44" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O44" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P44" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q44" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R44" t="n">
-        <v>0.4096165067315582</v>
+        <v>0.6695696033380315</v>
       </c>
       <c r="S44" t="n">
-        <v>0.9566057207181253</v>
+        <v>1.611135749027525</v>
       </c>
       <c r="T44" t="b">
         <v>0</v>
@@ -6698,60 +6698,60 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>S001,S003,S007,S011,S014,S015</t>
+          <t>S001,S006</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>S002,S004,S005,S009</t>
+          <t>S002,S003,S004,S005,S007,S009,S015</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>S006,S008,S010,S012,S013</t>
+          <t>S008,S010,S011,S012,S013,S014</t>
         </is>
       </c>
       <c r="G45" t="n">
         <v>8</v>
       </c>
       <c r="H45" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I45" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J45" t="n">
         <v>10</v>
       </c>
       <c r="K45" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L45" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M45" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N45" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O45" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="P45" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="Q45" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="R45" t="n">
-        <v>0.09938538711884903</v>
+        <v>0.5622943733758352</v>
       </c>
       <c r="S45" t="n">
-        <v>0.2215176338466955</v>
+        <v>1.373325564678237</v>
       </c>
       <c r="T45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U45" t="b">
         <v>0</v>
@@ -6773,21 +6773,21 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>S001,S006,S008</t>
+          <t>S001,S008,S010,S012,S013</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>S002,S003,S004,S005,S007,S009,S011,S014,S015</t>
+          <t>S002,S003,S004,S005,S006,S007,S009,S015</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>S010,S012,S013</t>
+          <t>S011,S014</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H46" t="n">
         <v>4</v>
@@ -6802,28 +6802,28 @@
         <v>6</v>
       </c>
       <c r="L46" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M46" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N46" t="n">
         <v>7</v>
       </c>
       <c r="O46" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="P46" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q46" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R46" t="n">
-        <v>0.6347557967747837</v>
+        <v>0.5486687199232557</v>
       </c>
       <c r="S46" t="n">
-        <v>1.373773948289412</v>
+        <v>1.333567877776596</v>
       </c>
       <c r="T46" t="b">
         <v>0</v>
@@ -6848,57 +6848,57 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>S001,S006</t>
+          <t>S001,S008</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>S002,S003,S004,S005,S007,S008,S009,S011,S014,S015</t>
+          <t>S002,S003,S004,S005,S006,S007,S009,S010,S012,S013,S015</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>S010,S012,S013</t>
+          <t>S011,S014</t>
         </is>
       </c>
       <c r="G47" t="n">
+        <v>6</v>
+      </c>
+      <c r="H47" t="n">
+        <v>4</v>
+      </c>
+      <c r="I47" t="n">
+        <v>4</v>
+      </c>
+      <c r="J47" t="n">
         <v>7</v>
       </c>
-      <c r="H47" t="n">
-        <v>3</v>
-      </c>
-      <c r="I47" t="n">
-        <v>4</v>
-      </c>
-      <c r="J47" t="n">
-        <v>9</v>
-      </c>
       <c r="K47" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L47" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M47" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N47" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O47" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="P47" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q47" t="n">
         <v>14</v>
       </c>
-      <c r="Q47" t="n">
-        <v>12</v>
-      </c>
       <c r="R47" t="n">
-        <v>0.8286680558474645</v>
+        <v>0.7603872843269841</v>
       </c>
       <c r="S47" t="n">
-        <v>1.875824985440784</v>
+        <v>1.670751635369644</v>
       </c>
       <c r="T47" t="b">
         <v>0</v>
@@ -6923,27 +6923,27 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>S001,S006,S010,S012,S013</t>
+          <t>S001,S008,S011,S014</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>S002,S003,S004,S005,S007,S009,S011,S014,S015</t>
+          <t>S002,S003,S004,S005,S006,S007,S009,S015</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>S008</t>
+          <t>S010,S012,S013</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H48" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I48" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J48" t="n">
         <v>9</v>
@@ -6952,28 +6952,28 @@
         <v>6</v>
       </c>
       <c r="L48" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M48" t="n">
         <v>6</v>
       </c>
       <c r="N48" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O48" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="P48" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="Q48" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="R48" t="n">
-        <v>0.6646061944049517</v>
+        <v>0.4752932889093467</v>
       </c>
       <c r="S48" t="n">
-        <v>1.588478371760742</v>
+        <v>1.131918280534298</v>
       </c>
       <c r="T48" t="b">
         <v>0</v>
@@ -6998,57 +6998,57 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>S001,S006</t>
+          <t>S001,S008</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>S002,S003,S004,S005,S007,S009,S010,S011,S012,S013,S014,S015</t>
+          <t>S002,S003,S004,S005,S006,S007,S009,S011,S014,S015</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>S008</t>
+          <t>S010,S012,S013</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H49" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I49" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J49" t="n">
+        <v>8</v>
+      </c>
+      <c r="K49" t="n">
+        <v>6</v>
+      </c>
+      <c r="L49" t="n">
+        <v>6</v>
+      </c>
+      <c r="M49" t="n">
+        <v>6</v>
+      </c>
+      <c r="N49" t="n">
         <v>7</v>
       </c>
-      <c r="K49" t="n">
-        <v>6</v>
-      </c>
-      <c r="L49" t="n">
-        <v>5</v>
-      </c>
-      <c r="M49" t="n">
-        <v>4</v>
-      </c>
-      <c r="N49" t="n">
-        <v>5</v>
-      </c>
       <c r="O49" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="P49" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="Q49" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="R49" t="n">
-        <v>0.9639172005371189</v>
+        <v>0.6778589315578962</v>
       </c>
       <c r="S49" t="n">
-        <v>2.065147167881025</v>
+        <v>1.456342928229391</v>
       </c>
       <c r="T49" t="b">
         <v>0</v>
@@ -7073,27 +7073,27 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>S001,S006</t>
+          <t>S001,S008</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>S002,S003,S004,S005,S007,S009,S011,S014,S015</t>
+          <t>S002,S003,S004,S005,S006,S007,S009,S015</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>S008,S010,S012,S013</t>
+          <t>S010,S011,S012,S013,S014</t>
         </is>
       </c>
       <c r="G50" t="n">
         <v>7</v>
       </c>
       <c r="H50" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I50" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J50" t="n">
         <v>9</v>
@@ -7102,28 +7102,28 @@
         <v>6</v>
       </c>
       <c r="L50" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M50" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N50" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O50" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="P50" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="Q50" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="R50" t="n">
-        <v>0.6744126952711444</v>
+        <v>0.5279954574115784</v>
       </c>
       <c r="S50" t="n">
-        <v>1.626116340811176</v>
+        <v>1.228799808231996</v>
       </c>
       <c r="T50" t="b">
         <v>0</v>
@@ -7148,57 +7148,57 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>S001,S008</t>
+          <t>S001,S010,S012,S013</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>S002,S003,S004,S005,S006,S007,S009,S011,S014,S015</t>
+          <t>S002,S003,S004,S005,S006,S007,S008,S009,S015</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>S010,S012,S013</t>
+          <t>S011,S014</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H51" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I51" t="n">
         <v>4</v>
       </c>
       <c r="J51" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K51" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L51" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M51" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N51" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O51" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="P51" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Q51" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="R51" t="n">
-        <v>0.7385609245528141</v>
+        <v>0.6652467287913875</v>
       </c>
       <c r="S51" t="n">
-        <v>1.609707075437576</v>
+        <v>1.532290064206986</v>
       </c>
       <c r="T51" t="b">
         <v>0</v>
@@ -7228,12 +7228,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>S002,S003,S004,S005,S006,S007,S008,S009,S011,S014,S015</t>
+          <t>S002,S003,S004,S005,S006,S007,S008,S009,S010,S012,S013,S015</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>S010,S012,S013</t>
+          <t>S011,S014</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7246,37 +7246,37 @@
         <v>4</v>
       </c>
       <c r="J52" t="n">
+        <v>7</v>
+      </c>
+      <c r="K52" t="n">
+        <v>4</v>
+      </c>
+      <c r="L52" t="n">
+        <v>6</v>
+      </c>
+      <c r="M52" t="n">
+        <v>3</v>
+      </c>
+      <c r="N52" t="n">
+        <v>4</v>
+      </c>
+      <c r="O52" t="n">
+        <v>36</v>
+      </c>
+      <c r="P52" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q52" t="n">
         <v>8</v>
       </c>
-      <c r="K52" t="n">
-        <v>4</v>
-      </c>
-      <c r="L52" t="n">
-        <v>5</v>
-      </c>
-      <c r="M52" t="n">
-        <v>4</v>
-      </c>
-      <c r="N52" t="n">
-        <v>5</v>
-      </c>
-      <c r="O52" t="n">
-        <v>38</v>
-      </c>
-      <c r="P52" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>9</v>
-      </c>
       <c r="R52" t="n">
-        <v>0.9462292757463852</v>
+        <v>1.012549559967447</v>
       </c>
       <c r="S52" t="n">
-        <v>2.184187251356667</v>
+        <v>2.280222974653832</v>
       </c>
       <c r="T52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U52" t="b">
         <v>0</v>
@@ -7298,57 +7298,57 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>S001,S010,S012,S013</t>
+          <t>S001,S011,S014</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>S002,S003,S004,S005,S006,S007,S009,S011,S014,S015</t>
+          <t>S002,S003,S004,S005,S006,S007,S008,S009,S015</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>S008</t>
+          <t>S010,S012,S013</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H53" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I53" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J53" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K53" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L53" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M53" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N53" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O53" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="P53" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Q53" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R53" t="n">
-        <v>0.7505639056510127</v>
+        <v>0.6550402272097345</v>
       </c>
       <c r="S53" t="n">
-        <v>1.734580635801237</v>
+        <v>1.404576131096767</v>
       </c>
       <c r="T53" t="b">
         <v>0</v>
@@ -7378,31 +7378,31 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>S002,S003,S004,S005,S006,S007,S009,S010,S011,S012,S013,S014,S015</t>
+          <t>S002,S003,S004,S005,S006,S007,S008,S009,S011,S014,S015</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>S008</t>
+          <t>S010,S012,S013</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H54" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I54" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J54" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K54" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L54" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M54" t="n">
         <v>4</v>
@@ -7411,22 +7411,22 @@
         <v>5</v>
       </c>
       <c r="O54" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="P54" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Q54" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="R54" t="n">
-        <v>1.080466785264617</v>
+        <v>0.92450199611477</v>
       </c>
       <c r="S54" t="n">
-        <v>2.386307912323859</v>
+        <v>2.146581169413636</v>
       </c>
       <c r="T54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U54" t="b">
         <v>0</v>
@@ -7453,52 +7453,52 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>S002,S003,S004,S005,S006,S007,S009,S011,S014,S015</t>
+          <t>S002,S003,S004,S005,S006,S007,S008,S009,S015</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>S008,S010,S012,S013</t>
+          <t>S010,S011,S012,S013,S014</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H55" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I55" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J55" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K55" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L55" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M55" t="n">
         <v>4</v>
       </c>
       <c r="N55" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O55" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P55" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q55" t="n">
         <v>13</v>
       </c>
       <c r="R55" t="n">
-        <v>0.7921169424850734</v>
+        <v>0.7851809818917693</v>
       </c>
       <c r="S55" t="n">
-        <v>1.918320868892166</v>
+        <v>1.900505934726088</v>
       </c>
       <c r="T55" t="b">
         <v>0</v>
@@ -7523,24 +7523,24 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>S001,S008,S010,S012,S013</t>
+          <t>S001,S010,S011,S012,S013,S014</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>S002,S003,S004,S005,S007,S009,S011,S014,S015</t>
+          <t>S002,S003,S004,S005,S006,S007,S009,S015</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>S006</t>
+          <t>S008</t>
         </is>
       </c>
       <c r="G56" t="n">
         <v>7</v>
       </c>
       <c r="H56" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I56" t="n">
         <v>4</v>
@@ -7552,28 +7552,28 @@
         <v>6</v>
       </c>
       <c r="L56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M56" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N56" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O56" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="P56" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q56" t="n">
         <v>19</v>
       </c>
-      <c r="Q56" t="n">
-        <v>16</v>
-      </c>
       <c r="R56" t="n">
-        <v>0.7154908466887696</v>
+        <v>0.5578646989460752</v>
       </c>
       <c r="S56" t="n">
-        <v>1.750989901174837</v>
+        <v>1.353594619322043</v>
       </c>
       <c r="T56" t="b">
         <v>0</v>
@@ -7598,57 +7598,57 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>S001,S008</t>
+          <t>S001,S010,S012,S013</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>S002,S003,S004,S005,S007,S009,S010,S011,S012,S013,S014,S015</t>
+          <t>S002,S003,S004,S005,S006,S007,S009,S011,S014,S015</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>S006</t>
+          <t>S008</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H57" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I57" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J57" t="n">
+        <v>8</v>
+      </c>
+      <c r="K57" t="n">
+        <v>6</v>
+      </c>
+      <c r="L57" t="n">
+        <v>6</v>
+      </c>
+      <c r="M57" t="n">
+        <v>6</v>
+      </c>
+      <c r="N57" t="n">
         <v>7</v>
       </c>
-      <c r="K57" t="n">
-        <v>6</v>
-      </c>
-      <c r="L57" t="n">
-        <v>5</v>
-      </c>
-      <c r="M57" t="n">
-        <v>4</v>
-      </c>
-      <c r="N57" t="n">
-        <v>5</v>
-      </c>
       <c r="O57" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="P57" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="Q57" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="R57" t="n">
-        <v>0.9723576860502759</v>
+        <v>0.6877468647153563</v>
       </c>
       <c r="S57" t="n">
-        <v>2.202395162876177</v>
+        <v>1.581137739319439</v>
       </c>
       <c r="T57" t="b">
         <v>0</v>
@@ -7673,24 +7673,24 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>S001,S008</t>
+          <t>S001,S010,S012,S013</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>S002,S003,S004,S005,S007,S009,S011,S014,S015</t>
+          <t>S002,S003,S004,S005,S006,S007,S009,S015</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>S006,S010,S012,S013</t>
+          <t>S008,S011,S014</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H58" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I58" t="n">
         <v>4</v>
@@ -7702,28 +7702,28 @@
         <v>6</v>
       </c>
       <c r="L58" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M58" t="n">
         <v>6</v>
       </c>
       <c r="N58" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O58" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="P58" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q58" t="n">
         <v>21</v>
       </c>
-      <c r="Q58" t="n">
-        <v>18</v>
-      </c>
       <c r="R58" t="n">
-        <v>0.6416109282057301</v>
+        <v>0.4573663539740532</v>
       </c>
       <c r="S58" t="n">
-        <v>1.463604811397081</v>
+        <v>1.01334321132843</v>
       </c>
       <c r="T58" t="b">
         <v>0</v>
@@ -7748,57 +7748,57 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>S001,S010,S012,S013</t>
+          <t>S001,S011,S014</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>S002,S003,S004,S005,S007,S008,S009,S011,S014,S015</t>
+          <t>S002,S003,S004,S005,S006,S007,S009,S010,S012,S013,S015</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>S006</t>
+          <t>S008</t>
         </is>
       </c>
       <c r="G59" t="n">
+        <v>6</v>
+      </c>
+      <c r="H59" t="n">
+        <v>4</v>
+      </c>
+      <c r="I59" t="n">
+        <v>4</v>
+      </c>
+      <c r="J59" t="n">
         <v>7</v>
       </c>
-      <c r="H59" t="n">
-        <v>3</v>
-      </c>
-      <c r="I59" t="n">
-        <v>4</v>
-      </c>
-      <c r="J59" t="n">
-        <v>9</v>
-      </c>
       <c r="K59" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L59" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M59" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N59" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O59" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="P59" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q59" t="n">
         <v>14</v>
       </c>
-      <c r="Q59" t="n">
-        <v>12</v>
-      </c>
       <c r="R59" t="n">
-        <v>0.8495072316543854</v>
+        <v>0.7608442913652157</v>
       </c>
       <c r="S59" t="n">
-        <v>2.007603552595806</v>
+        <v>1.678747146093721</v>
       </c>
       <c r="T59" t="b">
         <v>0</v>
@@ -7828,58 +7828,58 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>S002,S003,S004,S005,S007,S008,S009,S010,S011,S012,S013,S014,S015</t>
+          <t>S002,S003,S004,S005,S006,S007,S009,S010,S011,S012,S013,S014,S015</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>S006</t>
+          <t>S008</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J60" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K60" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L60" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M60" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N60" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O60" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="P60" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="Q60" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="R60" t="n">
-        <v>1.190790358782802</v>
+        <v>1.028009714530461</v>
       </c>
       <c r="S60" t="n">
-        <v>2.538335928555482</v>
+        <v>2.30687356312193</v>
       </c>
       <c r="T60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -7903,55 +7903,55 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>S002,S003,S004,S005,S007,S008,S009,S011,S014,S015</t>
+          <t>S002,S003,S004,S005,S006,S007,S009,S010,S012,S013,S015</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>S006,S010,S012,S013</t>
+          <t>S008,S011,S014</t>
         </is>
       </c>
       <c r="G61" t="n">
         <v>6</v>
       </c>
       <c r="H61" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I61" t="n">
         <v>4</v>
       </c>
       <c r="J61" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K61" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L61" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M61" t="n">
         <v>4</v>
       </c>
       <c r="N61" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O61" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="P61" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q61" t="n">
         <v>13</v>
       </c>
-      <c r="Q61" t="n">
-        <v>11</v>
-      </c>
       <c r="R61" t="n">
-        <v>0.8543479961115685</v>
+        <v>0.8060050884543795</v>
       </c>
       <c r="S61" t="n">
-        <v>2.030006118398725</v>
+        <v>1.942598623423373</v>
       </c>
       <c r="T61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U61" t="b">
         <v>0</v>
@@ -7973,27 +7973,27 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>S001,S010,S012,S013</t>
+          <t>S001,S011,S014</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>S002,S003,S004,S005,S007,S009,S011,S014,S015</t>
+          <t>S002,S003,S004,S005,S006,S007,S009,S015</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>S006,S008</t>
+          <t>S008,S010,S012,S013</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H62" t="n">
         <v>4</v>
       </c>
       <c r="I62" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J62" t="n">
         <v>9</v>
@@ -8002,28 +8002,28 @@
         <v>6</v>
       </c>
       <c r="L62" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M62" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N62" t="n">
         <v>7</v>
       </c>
       <c r="O62" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="P62" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Q62" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="R62" t="n">
-        <v>0.6392385982325898</v>
+        <v>0.5178542080260936</v>
       </c>
       <c r="S62" t="n">
-        <v>1.442376107720247</v>
+        <v>1.209920598183394</v>
       </c>
       <c r="T62" t="b">
         <v>0</v>
@@ -8053,52 +8053,52 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>S002,S003,S004,S005,S007,S009,S010,S011,S012,S013,S014,S015</t>
+          <t>S002,S003,S004,S005,S006,S007,S009,S011,S014,S015</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>S006,S008</t>
+          <t>S008,S010,S012,S013</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H63" t="n">
         <v>4</v>
       </c>
       <c r="I63" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J63" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K63" t="n">
         <v>6</v>
       </c>
       <c r="L63" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M63" t="n">
         <v>4</v>
       </c>
       <c r="N63" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O63" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="P63" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="Q63" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="R63" t="n">
-        <v>0.9750669911127314</v>
+        <v>0.7923080271771951</v>
       </c>
       <c r="S63" t="n">
-        <v>2.225727540102441</v>
+        <v>1.916332366549578</v>
       </c>
       <c r="T63" t="b">
         <v>0</v>
@@ -8128,22 +8128,22 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>S002,S003,S004,S005,S007,S009,S011,S014,S015</t>
+          <t>S002,S003,S004,S005,S006,S007,S009,S015</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>S006,S008,S010,S012,S013</t>
+          <t>S008,S010,S011,S012,S013,S014</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H64" t="n">
         <v>4</v>
       </c>
       <c r="I64" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J64" t="n">
         <v>9</v>
@@ -8152,7 +8152,7 @@
         <v>6</v>
       </c>
       <c r="L64" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M64" t="n">
         <v>4</v>
@@ -8161,19 +8161,19 @@
         <v>6</v>
       </c>
       <c r="O64" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="P64" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q64" t="n">
         <v>17</v>
       </c>
-      <c r="Q64" t="n">
-        <v>14</v>
-      </c>
       <c r="R64" t="n">
-        <v>0.7236719172252758</v>
+        <v>0.6865934487890636</v>
       </c>
       <c r="S64" t="n">
-        <v>1.772218604851671</v>
+        <v>1.67852218220029</v>
       </c>
       <c r="T64" t="b">
         <v>0</v>
@@ -8198,24 +8198,24 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>S001,S006,S008,S010,S012,S013</t>
+          <t>S001,S008,S010,S011,S012,S013,S014</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>S002,S004,S005,S009</t>
+          <t>S002,S003,S004,S005,S007,S009,S015</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>S003,S007,S011,S014,S015</t>
+          <t>S006</t>
         </is>
       </c>
       <c r="G65" t="n">
         <v>8</v>
       </c>
       <c r="H65" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I65" t="n">
         <v>4</v>
@@ -8224,34 +8224,34 @@
         <v>10</v>
       </c>
       <c r="K65" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L65" t="n">
         <v>6</v>
       </c>
       <c r="M65" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N65" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O65" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="P65" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="Q65" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="R65" t="n">
-        <v>0.04122748025347911</v>
+        <v>0.6285924292823607</v>
       </c>
       <c r="S65" t="n">
-        <v>0.08838506012045139</v>
+        <v>1.503751292476549</v>
       </c>
       <c r="T65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U65" t="b">
         <v>0</v>
@@ -8273,57 +8273,57 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>S001,S006,S008</t>
+          <t>S001,S008,S010,S012,S013</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>S002,S004,S005,S009,S010,S012,S013</t>
+          <t>S002,S003,S004,S005,S007,S009,S011,S014,S015</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>S003,S007,S011,S014,S015</t>
+          <t>S006</t>
         </is>
       </c>
       <c r="G66" t="n">
         <v>7</v>
       </c>
       <c r="H66" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I66" t="n">
         <v>4</v>
       </c>
       <c r="J66" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K66" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L66" t="n">
         <v>6</v>
       </c>
       <c r="M66" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N66" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O66" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="P66" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="Q66" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="R66" t="n">
-        <v>0.3440840905756985</v>
+        <v>0.7117578398730997</v>
       </c>
       <c r="S66" t="n">
-        <v>0.8373336168096963</v>
+        <v>1.741561476825837</v>
       </c>
       <c r="T66" t="b">
         <v>0</v>
@@ -8348,60 +8348,60 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>S001,S006,S008</t>
+          <t>S001,S008,S010,S012,S013</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>S002,S004,S005,S009</t>
+          <t>S002,S003,S004,S005,S007,S009,S015</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>S003,S007,S010,S011,S012,S013,S014,S015</t>
+          <t>S006,S011,S014</t>
         </is>
       </c>
       <c r="G67" t="n">
         <v>8</v>
       </c>
       <c r="H67" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I67" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J67" t="n">
         <v>10</v>
       </c>
       <c r="K67" t="n">
+        <v>6</v>
+      </c>
+      <c r="L67" t="n">
+        <v>6</v>
+      </c>
+      <c r="M67" t="n">
+        <v>5</v>
+      </c>
+      <c r="N67" t="n">
         <v>7</v>
       </c>
-      <c r="L67" t="n">
-        <v>6</v>
-      </c>
-      <c r="M67" t="n">
-        <v>6</v>
-      </c>
-      <c r="N67" t="n">
-        <v>8</v>
-      </c>
       <c r="O67" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="P67" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Q67" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="R67" t="n">
-        <v>0.3439345368739236</v>
+        <v>0.4317103865167037</v>
       </c>
       <c r="S67" t="n">
-        <v>0.8205955539608775</v>
+        <v>1.044232850595422</v>
       </c>
       <c r="T67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U67" t="b">
         <v>0</v>
@@ -8423,31 +8423,31 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>S001,S006,S010,S012,S013</t>
+          <t>S001,S008,S011,S014</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>S002,S004,S005,S008,S009</t>
+          <t>S002,S003,S004,S005,S007,S009,S010,S012,S013,S015</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>S003,S007,S011,S014,S015</t>
+          <t>S006</t>
         </is>
       </c>
       <c r="G68" t="n">
+        <v>7</v>
+      </c>
+      <c r="H68" t="n">
+        <v>5</v>
+      </c>
+      <c r="I68" t="n">
+        <v>4</v>
+      </c>
+      <c r="J68" t="n">
         <v>8</v>
       </c>
-      <c r="H68" t="n">
-        <v>5</v>
-      </c>
-      <c r="I68" t="n">
-        <v>4</v>
-      </c>
-      <c r="J68" t="n">
-        <v>10</v>
-      </c>
       <c r="K68" t="n">
         <v>6</v>
       </c>
@@ -8455,25 +8455,25 @@
         <v>6</v>
       </c>
       <c r="M68" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N68" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O68" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="P68" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="Q68" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="R68" t="n">
-        <v>0.2113797421508881</v>
+        <v>0.7235574802842343</v>
       </c>
       <c r="S68" t="n">
-        <v>0.5167541204128716</v>
+        <v>1.767827733699632</v>
       </c>
       <c r="T68" t="b">
         <v>0</v>
@@ -8498,31 +8498,31 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>S001,S006</t>
+          <t>S001,S008</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>S002,S004,S005,S008,S009,S010,S012,S013</t>
+          <t>S002,S003,S004,S005,S007,S009,S010,S011,S012,S013,S014,S015</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>S003,S007,S011,S014,S015</t>
+          <t>S006</t>
         </is>
       </c>
       <c r="G69" t="n">
+        <v>5</v>
+      </c>
+      <c r="H69" t="n">
+        <v>5</v>
+      </c>
+      <c r="I69" t="n">
+        <v>4</v>
+      </c>
+      <c r="J69" t="n">
         <v>7</v>
       </c>
-      <c r="H69" t="n">
-        <v>5</v>
-      </c>
-      <c r="I69" t="n">
-        <v>4</v>
-      </c>
-      <c r="J69" t="n">
-        <v>8</v>
-      </c>
       <c r="K69" t="n">
         <v>6</v>
       </c>
@@ -8536,19 +8536,19 @@
         <v>5</v>
       </c>
       <c r="O69" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="P69" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="Q69" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="R69" t="n">
-        <v>0.5542780902566429</v>
+        <v>0.9216336261350034</v>
       </c>
       <c r="S69" t="n">
-        <v>1.343994245781252</v>
+        <v>2.121965878072332</v>
       </c>
       <c r="T69" t="b">
         <v>0</v>
@@ -8573,31 +8573,31 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>S001,S006</t>
+          <t>S001,S008</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>S002,S004,S005,S008,S009</t>
+          <t>S002,S003,S004,S005,S007,S009,S010,S012,S013,S015</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>S003,S007,S010,S011,S012,S013,S014,S015</t>
+          <t>S006,S011,S014</t>
         </is>
       </c>
       <c r="G70" t="n">
+        <v>6</v>
+      </c>
+      <c r="H70" t="n">
+        <v>5</v>
+      </c>
+      <c r="I70" t="n">
+        <v>4</v>
+      </c>
+      <c r="J70" t="n">
         <v>8</v>
       </c>
-      <c r="H70" t="n">
-        <v>5</v>
-      </c>
-      <c r="I70" t="n">
-        <v>3</v>
-      </c>
-      <c r="J70" t="n">
-        <v>10</v>
-      </c>
       <c r="K70" t="n">
         <v>6</v>
       </c>
@@ -8605,25 +8605,25 @@
         <v>6</v>
       </c>
       <c r="M70" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N70" t="n">
         <v>6</v>
       </c>
       <c r="O70" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="P70" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Q70" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="R70" t="n">
-        <v>0.5233365322408262</v>
+        <v>0.6509560165217758</v>
       </c>
       <c r="S70" t="n">
-        <v>1.161418499329498</v>
+        <v>1.395723109534383</v>
       </c>
       <c r="T70" t="b">
         <v>0</v>
@@ -8648,17 +8648,17 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>S001,S006,S010,S012,S013</t>
+          <t>S001,S008,S011,S014</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>S002,S004,S005,S009</t>
+          <t>S002,S003,S004,S005,S007,S009,S015</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>S003,S007,S008,S011,S014,S015</t>
+          <t>S006,S010,S012,S013</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8668,13 +8668,13 @@
         <v>5</v>
       </c>
       <c r="I71" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J71" t="n">
         <v>10</v>
       </c>
       <c r="K71" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L71" t="n">
         <v>6</v>
@@ -8683,25 +8683,25 @@
         <v>6</v>
       </c>
       <c r="N71" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O71" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P71" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q71" t="n">
         <v>24</v>
       </c>
-      <c r="Q71" t="n">
-        <v>21</v>
-      </c>
       <c r="R71" t="n">
-        <v>0.1903759690866769</v>
+        <v>0.3661219975558484</v>
       </c>
       <c r="S71" t="n">
-        <v>0.4260779998376464</v>
+        <v>0.8544522417782328</v>
       </c>
       <c r="T71" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U71" t="b">
         <v>0</v>
@@ -8723,60 +8723,60 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>S001,S006</t>
+          <t>S001,S008</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>S002,S004,S005,S009,S010,S012,S013</t>
+          <t>S002,S003,S004,S005,S007,S009,S011,S014,S015</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>S003,S007,S008,S011,S014,S015</t>
+          <t>S006,S010,S012,S013</t>
         </is>
       </c>
       <c r="G72" t="n">
+        <v>6</v>
+      </c>
+      <c r="H72" t="n">
+        <v>5</v>
+      </c>
+      <c r="I72" t="n">
+        <v>5</v>
+      </c>
+      <c r="J72" t="n">
+        <v>9</v>
+      </c>
+      <c r="K72" t="n">
+        <v>6</v>
+      </c>
+      <c r="L72" t="n">
+        <v>6</v>
+      </c>
+      <c r="M72" t="n">
+        <v>6</v>
+      </c>
+      <c r="N72" t="n">
         <v>7</v>
       </c>
-      <c r="H72" t="n">
-        <v>5</v>
-      </c>
-      <c r="I72" t="n">
-        <v>4</v>
-      </c>
-      <c r="J72" t="n">
-        <v>8</v>
-      </c>
-      <c r="K72" t="n">
-        <v>5</v>
-      </c>
-      <c r="L72" t="n">
-        <v>6</v>
-      </c>
-      <c r="M72" t="n">
-        <v>4</v>
-      </c>
-      <c r="N72" t="n">
-        <v>5</v>
-      </c>
       <c r="O72" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="P72" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="Q72" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R72" t="n">
-        <v>0.5209455887840178</v>
+        <v>0.5793063447470002</v>
       </c>
       <c r="S72" t="n">
-        <v>1.191748687473833</v>
+        <v>1.310332800964151</v>
       </c>
       <c r="T72" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U72" t="b">
         <v>0</v>
@@ -8798,57 +8798,57 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>S001,S006</t>
+          <t>S001,S008</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>S002,S004,S005,S009</t>
+          <t>S002,S003,S004,S005,S007,S009,S015</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>S003,S007,S008,S010,S011,S012,S013,S014,S015</t>
+          <t>S006,S010,S011,S012,S013,S014</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H73" t="n">
         <v>5</v>
       </c>
       <c r="I73" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J73" t="n">
         <v>10</v>
       </c>
       <c r="K73" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L73" t="n">
         <v>6</v>
       </c>
       <c r="M73" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N73" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O73" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="P73" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="Q73" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="R73" t="n">
-        <v>0.5468875977352561</v>
+        <v>0.4462963659170654</v>
       </c>
       <c r="S73" t="n">
-        <v>1.308190501363645</v>
+        <v>1.082789680966755</v>
       </c>
       <c r="T73" t="b">
         <v>0</v>
@@ -8873,57 +8873,57 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>S001,S008,S010,S012,S013</t>
+          <t>S001,S010,S011,S012,S013,S014</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>S002,S004,S005,S006,S009</t>
+          <t>S002,S003,S004,S005,S007,S008,S009,S015</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>S003,S007,S011,S014,S015</t>
+          <t>S006</t>
         </is>
       </c>
       <c r="G74" t="n">
         <v>8</v>
       </c>
       <c r="H74" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I74" t="n">
         <v>4</v>
       </c>
       <c r="J74" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K74" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L74" t="n">
         <v>6</v>
       </c>
       <c r="M74" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N74" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O74" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="P74" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="Q74" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="R74" t="n">
-        <v>0.1423932062168569</v>
+        <v>0.7024963665091698</v>
       </c>
       <c r="S74" t="n">
-        <v>0.3453529196988028</v>
+        <v>1.719660914051303</v>
       </c>
       <c r="T74" t="b">
         <v>0</v>
@@ -8948,57 +8948,57 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>S001,S008</t>
+          <t>S001,S010,S012,S013</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>S002,S004,S005,S006,S009,S010,S012,S013</t>
+          <t>S002,S003,S004,S005,S007,S008,S009,S011,S014,S015</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>S003,S007,S011,S014,S015</t>
+          <t>S006</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H75" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I75" t="n">
         <v>4</v>
       </c>
       <c r="J75" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K75" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L75" t="n">
         <v>6</v>
       </c>
       <c r="M75" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N75" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O75" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="P75" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="Q75" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="R75" t="n">
-        <v>0.4574664163952745</v>
+        <v>0.8268325724522733</v>
       </c>
       <c r="S75" t="n">
-        <v>1.116430718984829</v>
+        <v>1.965736148738852</v>
       </c>
       <c r="T75" t="b">
         <v>0</v>
@@ -9023,57 +9023,57 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>S001,S008</t>
+          <t>S001,S010,S012,S013</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>S002,S004,S005,S006,S009</t>
+          <t>S002,S003,S004,S005,S007,S008,S009,S015</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>S003,S007,S010,S011,S012,S013,S014,S015</t>
+          <t>S006,S011,S014</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H76" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J76" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K76" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L76" t="n">
         <v>6</v>
       </c>
       <c r="M76" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N76" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O76" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="P76" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="Q76" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="R76" t="n">
-        <v>0.4267369922348933</v>
+        <v>0.5520836775682659</v>
       </c>
       <c r="S76" t="n">
-        <v>0.9553695374817991</v>
+        <v>1.233439054872759</v>
       </c>
       <c r="T76" t="b">
         <v>0</v>
@@ -9098,57 +9098,57 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>S001,S010,S012,S013</t>
+          <t>S001,S011,S014</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>S002,S004,S005,S006,S008,S009</t>
+          <t>S002,S003,S004,S005,S007,S008,S009,S010,S012,S013,S015</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>S003,S007,S011,S014,S015</t>
+          <t>S006</t>
         </is>
       </c>
       <c r="G77" t="n">
+        <v>7</v>
+      </c>
+      <c r="H77" t="n">
+        <v>3</v>
+      </c>
+      <c r="I77" t="n">
+        <v>4</v>
+      </c>
+      <c r="J77" t="n">
         <v>8</v>
       </c>
-      <c r="H77" t="n">
-        <v>4</v>
-      </c>
-      <c r="I77" t="n">
-        <v>4</v>
-      </c>
-      <c r="J77" t="n">
-        <v>9</v>
-      </c>
       <c r="K77" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L77" t="n">
         <v>6</v>
       </c>
       <c r="M77" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N77" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O77" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="P77" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="Q77" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="R77" t="n">
-        <v>0.321211719751036</v>
+        <v>0.9040650167543873</v>
       </c>
       <c r="S77" t="n">
-        <v>0.7861350151504087</v>
+        <v>2.090520839610793</v>
       </c>
       <c r="T77" t="b">
         <v>0</v>
@@ -9178,19 +9178,19 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>S002,S004,S005,S006,S008,S009,S010,S012,S013</t>
+          <t>S002,S003,S004,S005,S007,S008,S009,S010,S011,S012,S013,S014,S015</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>S003,S007,S011,S014,S015</t>
+          <t>S006</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H78" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I78" t="n">
         <v>4</v>
@@ -9199,37 +9199,37 @@
         <v>7</v>
       </c>
       <c r="K78" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L78" t="n">
         <v>6</v>
       </c>
       <c r="M78" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N78" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O78" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="P78" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="Q78" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="R78" t="n">
-        <v>0.6732259323245438</v>
+        <v>1.183290165105396</v>
       </c>
       <c r="S78" t="n">
-        <v>1.637795549019265</v>
+        <v>2.522834443819205</v>
       </c>
       <c r="T78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -9253,55 +9253,55 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>S002,S004,S005,S006,S008,S009</t>
+          <t>S002,S003,S004,S005,S007,S008,S009,S010,S012,S013,S015</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>S003,S007,S010,S011,S012,S013,S014,S015</t>
+          <t>S006,S011,S014</t>
         </is>
       </c>
       <c r="G79" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H79" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I79" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J79" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K79" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L79" t="n">
         <v>6</v>
       </c>
       <c r="M79" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N79" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O79" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="P79" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="Q79" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="R79" t="n">
-        <v>0.6216443783802864</v>
+        <v>0.9079313074010422</v>
       </c>
       <c r="S79" t="n">
-        <v>1.333836439410196</v>
+        <v>2.114587696252023</v>
       </c>
       <c r="T79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U79" t="b">
         <v>0</v>
@@ -9323,30 +9323,30 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>S001,S010,S012,S013</t>
+          <t>S001,S011,S014</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>S002,S004,S005,S006,S009</t>
+          <t>S002,S003,S004,S005,S007,S008,S009,S015</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>S003,S007,S008,S011,S014,S015</t>
+          <t>S006,S010,S012,S013</t>
         </is>
       </c>
       <c r="G80" t="n">
         <v>8</v>
       </c>
       <c r="H80" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I80" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J80" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K80" t="n">
         <v>5</v>
@@ -9355,25 +9355,25 @@
         <v>6</v>
       </c>
       <c r="M80" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N80" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O80" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P80" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q80" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R80" t="n">
-        <v>0.2867127343574795</v>
+        <v>0.5541545319698296</v>
       </c>
       <c r="S80" t="n">
-        <v>0.6465439232639174</v>
+        <v>1.255150626429653</v>
       </c>
       <c r="T80" t="b">
         <v>0</v>
@@ -9403,25 +9403,25 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>S002,S004,S005,S006,S009,S010,S012,S013</t>
+          <t>S002,S003,S004,S005,S007,S008,S009,S011,S014,S015</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>S003,S007,S008,S011,S014,S015</t>
+          <t>S006,S010,S012,S013</t>
         </is>
       </c>
       <c r="G81" t="n">
         <v>6</v>
       </c>
       <c r="H81" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I81" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J81" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K81" t="n">
         <v>5</v>
@@ -9436,22 +9436,22 @@
         <v>5</v>
       </c>
       <c r="O81" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="P81" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q81" t="n">
         <v>14</v>
       </c>
-      <c r="Q81" t="n">
-        <v>12</v>
-      </c>
       <c r="R81" t="n">
-        <v>0.6344156996335978</v>
+        <v>0.8322121275501985</v>
       </c>
       <c r="S81" t="n">
-        <v>1.485549990711846</v>
+        <v>1.9886793337793</v>
       </c>
       <c r="T81" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U81" t="b">
         <v>0</v>
@@ -9478,25 +9478,25 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>S002,S004,S005,S006,S009</t>
+          <t>S002,S003,S004,S005,S007,S008,S009,S015</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>S003,S007,S008,S010,S011,S012,S013,S014,S015</t>
+          <t>S006,S010,S011,S012,S013,S014</t>
         </is>
       </c>
       <c r="G82" t="n">
         <v>7</v>
       </c>
       <c r="H82" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I82" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J82" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K82" t="n">
         <v>5</v>
@@ -9508,22 +9508,22 @@
         <v>4</v>
       </c>
       <c r="N82" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O82" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P82" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q82" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="R82" t="n">
-        <v>0.630705549817684</v>
+        <v>0.7114702386099567</v>
       </c>
       <c r="S82" t="n">
-        <v>1.449809757635844</v>
+        <v>1.742604099091751</v>
       </c>
       <c r="T82" t="b">
         <v>0</v>
@@ -9548,24 +9548,24 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>S001,S008,S010,S012,S013</t>
+          <t>S001,S010,S011,S012,S013,S014</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>S002,S004,S005,S009</t>
+          <t>S002,S003,S004,S005,S007,S009,S015</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>S003,S006,S007,S011,S014,S015</t>
+          <t>S006,S008</t>
         </is>
       </c>
       <c r="G83" t="n">
         <v>8</v>
       </c>
       <c r="H83" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I83" t="n">
         <v>4</v>
@@ -9574,31 +9574,31 @@
         <v>10</v>
       </c>
       <c r="K83" t="n">
+        <v>6</v>
+      </c>
+      <c r="L83" t="n">
+        <v>6</v>
+      </c>
+      <c r="M83" t="n">
+        <v>6</v>
+      </c>
+      <c r="N83" t="n">
         <v>7</v>
       </c>
-      <c r="L83" t="n">
-        <v>6</v>
-      </c>
-      <c r="M83" t="n">
-        <v>6</v>
-      </c>
-      <c r="N83" t="n">
-        <v>8</v>
-      </c>
       <c r="O83" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="P83" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="Q83" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="R83" t="n">
-        <v>0.1134318104425601</v>
+        <v>0.4400757269126518</v>
       </c>
       <c r="S83" t="n">
-        <v>0.2588551424834344</v>
+        <v>1.061574364791563</v>
       </c>
       <c r="T83" t="b">
         <v>0</v>
@@ -9623,33 +9623,33 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>S001,S008</t>
+          <t>S001,S010,S012,S013</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>S002,S004,S005,S009,S010,S012,S013</t>
+          <t>S002,S003,S004,S005,S007,S009,S011,S014,S015</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>S003,S006,S007,S011,S014,S015</t>
+          <t>S006,S008</t>
         </is>
       </c>
       <c r="G84" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H84" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I84" t="n">
         <v>4</v>
       </c>
       <c r="J84" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K84" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L84" t="n">
         <v>6</v>
@@ -9661,19 +9661,19 @@
         <v>7</v>
       </c>
       <c r="O84" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="P84" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q84" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R84" t="n">
-        <v>0.4219819149611615</v>
+        <v>0.5773216663240749</v>
       </c>
       <c r="S84" t="n">
-        <v>0.9768821678972628</v>
+        <v>1.289117484788958</v>
       </c>
       <c r="T84" t="b">
         <v>0</v>
@@ -9698,33 +9698,33 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>S001,S008</t>
+          <t>S001,S010,S012,S013</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>S002,S004,S005,S009</t>
+          <t>S002,S003,S004,S005,S007,S009,S015</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>S003,S006,S007,S010,S011,S012,S013,S014,S015</t>
+          <t>S006,S008,S011,S014</t>
         </is>
       </c>
       <c r="G85" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H85" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I85" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J85" t="n">
         <v>10</v>
       </c>
       <c r="K85" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L85" t="n">
         <v>6</v>
@@ -9736,22 +9736,22 @@
         <v>8</v>
       </c>
       <c r="O85" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="P85" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q85" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R85" t="n">
-        <v>0.4518077812396056</v>
+        <v>0.3699833746881406</v>
       </c>
       <c r="S85" t="n">
-        <v>1.090143521002721</v>
+        <v>0.8746101919503974</v>
       </c>
       <c r="T85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U85" t="b">
         <v>0</v>
@@ -9773,31 +9773,31 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>S001,S010,S012,S013</t>
+          <t>S001,S011,S014</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>S002,S004,S005,S008,S009</t>
+          <t>S002,S003,S004,S005,S007,S009,S010,S012,S013,S015</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>S003,S006,S007,S011,S014,S015</t>
+          <t>S006,S008</t>
         </is>
       </c>
       <c r="G86" t="n">
+        <v>7</v>
+      </c>
+      <c r="H86" t="n">
+        <v>4</v>
+      </c>
+      <c r="I86" t="n">
+        <v>4</v>
+      </c>
+      <c r="J86" t="n">
         <v>8</v>
       </c>
-      <c r="H86" t="n">
-        <v>4</v>
-      </c>
-      <c r="I86" t="n">
-        <v>4</v>
-      </c>
-      <c r="J86" t="n">
-        <v>10</v>
-      </c>
       <c r="K86" t="n">
         <v>6</v>
       </c>
@@ -9805,25 +9805,25 @@
         <v>6</v>
       </c>
       <c r="M86" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N86" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O86" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="P86" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="Q86" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="R86" t="n">
-        <v>0.2872288976841748</v>
+        <v>0.6508652303203688</v>
       </c>
       <c r="S86" t="n">
-        <v>0.6514445677816402</v>
+        <v>1.387727598810307</v>
       </c>
       <c r="T86" t="b">
         <v>0</v>
@@ -9853,16 +9853,16 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>S002,S004,S005,S008,S009,S010,S012,S013</t>
+          <t>S002,S003,S004,S005,S007,S009,S010,S011,S012,S013,S014,S015</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>S003,S006,S007,S011,S014,S015</t>
+          <t>S006,S008</t>
         </is>
       </c>
       <c r="G87" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H87" t="n">
         <v>4</v>
@@ -9871,7 +9871,7 @@
         <v>4</v>
       </c>
       <c r="J87" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K87" t="n">
         <v>6</v>
@@ -9886,19 +9886,19 @@
         <v>5</v>
       </c>
       <c r="O87" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="P87" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Q87" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="R87" t="n">
-        <v>0.6354065755716438</v>
+        <v>0.9251660969920291</v>
       </c>
       <c r="S87" t="n">
-        <v>1.490894897400258</v>
+        <v>2.145424479352391</v>
       </c>
       <c r="T87" t="b">
         <v>0</v>
@@ -9928,25 +9928,25 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>S002,S004,S005,S008,S009</t>
+          <t>S002,S003,S004,S005,S007,S009,S010,S012,S013,S015</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>S003,S006,S007,S010,S011,S012,S013,S014,S015</t>
+          <t>S006,S008,S011,S014</t>
         </is>
       </c>
       <c r="G88" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H88" t="n">
         <v>4</v>
       </c>
       <c r="I88" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J88" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K88" t="n">
         <v>6</v>
@@ -9961,19 +9961,19 @@
         <v>6</v>
       </c>
       <c r="O88" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="P88" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Q88" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="R88" t="n">
-        <v>0.6300036649680104</v>
+        <v>0.7316486900722589</v>
       </c>
       <c r="S88" t="n">
-        <v>1.444657011873896</v>
+        <v>1.790000314662347</v>
       </c>
       <c r="T88" t="b">
         <v>0</v>
@@ -9998,17 +9998,17 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>S001,S010,S012,S013</t>
+          <t>S001,S011,S014</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>S002,S004,S005,S009</t>
+          <t>S002,S003,S004,S005,S007,S009,S015</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>S003,S006,S007,S008,S011,S014,S015</t>
+          <t>S006,S008,S010,S012,S013</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -10018,37 +10018,37 @@
         <v>4</v>
       </c>
       <c r="I89" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J89" t="n">
         <v>10</v>
       </c>
       <c r="K89" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L89" t="n">
         <v>6</v>
       </c>
       <c r="M89" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N89" t="n">
         <v>7</v>
       </c>
       <c r="O89" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="P89" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q89" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R89" t="n">
-        <v>0.2942727390625447</v>
+        <v>0.4381333760766691</v>
       </c>
       <c r="S89" t="n">
-        <v>0.6954588945751836</v>
+        <v>1.065253084592807</v>
       </c>
       <c r="T89" t="b">
         <v>0</v>
@@ -10078,12 +10078,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>S002,S004,S005,S009,S010,S012,S013</t>
+          <t>S002,S003,S004,S005,S007,S009,S011,S014,S015</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>S003,S006,S007,S008,S011,S014,S015</t>
+          <t>S006,S008,S010,S012,S013</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -10093,13 +10093,13 @@
         <v>4</v>
       </c>
       <c r="I90" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J90" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K90" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L90" t="n">
         <v>6</v>
@@ -10108,22 +10108,22 @@
         <v>4</v>
       </c>
       <c r="N90" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O90" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="P90" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="Q90" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="R90" t="n">
-        <v>0.6187177082986217</v>
+        <v>0.7202512488718209</v>
       </c>
       <c r="S90" t="n">
-        <v>1.338649339092839</v>
+        <v>1.763734057788551</v>
       </c>
       <c r="T90" t="b">
         <v>0</v>
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>S002,S004,S005,S009</t>
+          <t>S002,S003,S004,S005,S007,S009,S015</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>S003,S006,S007,S008,S010,S011,S012,S013,S014,S015</t>
+          <t>S006,S008,S010,S011,S012,S013,S014</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -10168,13 +10168,13 @@
         <v>4</v>
       </c>
       <c r="I91" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J91" t="n">
         <v>10</v>
       </c>
       <c r="K91" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L91" t="n">
         <v>6</v>
@@ -10186,19 +10186,19 @@
         <v>6</v>
       </c>
       <c r="O91" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="P91" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q91" t="n">
         <v>18</v>
       </c>
-      <c r="Q91" t="n">
-        <v>15</v>
-      </c>
       <c r="R91" t="n">
-        <v>0.6602777427959259</v>
+        <v>0.6409417483223612</v>
       </c>
       <c r="S91" t="n">
-        <v>1.591429013908043</v>
+        <v>1.525923873439264</v>
       </c>
       <c r="T91" t="b">
         <v>0</v>
